--- a/data/naver_board_006800.xlsx
+++ b/data/naver_board_006800.xlsx
@@ -473,15 +473,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026.04.12 02:27</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>문득 궁금한게 있는데..</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>예전에 호박이가 안보이네
+극안티였는데 내 기억으로는..
+7만 초 중 후반때 설치고 다녔던 놈 인듯..
+요즘 왜 안보이지..
+금방이라도 상폐 당할것처럼 
+시끄럽게 떠들고 다녔던
+이상한놈 있었는데..
+포기하고 간겨?
+공매치다가..
+저 세상 사람됐는가?</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>문득 궁금한게 있는데.. 예전에 호박이가 안보이네
+극안티였는데 내 기억으로는..
+7만 초 중 후반때 설치고 다녔던 놈 인듯..
+요즘 왜 안보이지..
+금방이라도 상폐 당할것처럼 
+시끄럽게 떠들고 다녔던
+이상한놈 있었는데..
+포기하고 간겨?
+공매치다가..
+저 세상 사람됐는가?</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>417356366</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>2026.04.11 23:52</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>이란 1일 일정이라는 야기가 나오는데....[1]</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>뭐냐...정말이냐? 협상.....?
 혹시 아시는분??
@@ -489,16 +541,16 @@
 1일 더 연기설도 나오는중....</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>139</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>이란 1일 일정이라는 야기가 나오는데....[1] 뭐냐...정말이냐? 협상.....?
 혹시 아시는분??
@@ -506,22 +558,22 @@
 1일 더 연기설도 나오는중....</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>417355547</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026.04.11 22:50</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>&lt;공격예고&gt;이란국영TV는 미군함정이 호르무즈[2]</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>이란 국영 TV는 미군 함정이 호르무즈
 해협을 건널 경우 30분 이내에 공격받을 
@@ -529,16 +581,16 @@
 .</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>145</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>&lt;공격예고&gt;이란국영TV는 미군함정이 호르무즈[2] 이란 국영 TV는 미군 함정이 호르무즈
 해협을 건널 경우 30분 이내에 공격받을 
@@ -546,22 +598,22 @@
 .</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>417354945</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026.04.11 21:51</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>스페이스X, 통신사 M&amp;A 가능성 존재…美 인...[2]</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>아르테미스 무사귀환 하고
 스페이스x 상장전부터 주가 레벨업 작업
@@ -570,16 +622,16 @@
 나는구나</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>11</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>370</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>스페이스X, 통신사 M&amp;A 가능성 존재…美 인...[2] 아르테미스 무사귀환 하고
 스페이스x 상장전부터 주가 레벨업 작업
@@ -588,90 +640,90 @@
 나는구나</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>417354153</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026.04.11 21:08</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>공매도 금지법 상정 못하나 진짜[1]</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>답답합니다</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>60</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>공매도 금지법 상정 못하나 진짜[1] 답답합니다</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>417353572</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026.04.11 21:05</t>
+          <t>2026.04.11 21:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이평선이 정배열이 되었군요</t>
+          <t>공매도 금지법 상정 못하나 진짜[1]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1일 차트 정배열 완료 이제 상승확률이 올라가겠군요</t>
+          <t>답답합니다</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>이평선이 정배열이 되었군요 1일 차트 정배열 완료 이제 상승확률이 올라가겠군요</t>
+          <t>공매도 금지법 상정 못하나 진짜[1] 답답합니다</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>417353541</v>
+        <v>417353572</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026.04.11 21:05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>이평선이 정배열이 되었군요</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1일 차트 정배열 완료 이제 상승확률이 올라가겠군요</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>76</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>이평선이 정배열이 되었군요 1일 차트 정배열 완료 이제 상승확률이 올라가겠군요</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>417353541</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>2026.04.11 20:51</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>14일 이스라엘 레바논 협상...</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">이쪽이 끝나야.....??
 미 이란 협상이 본격적 시작될듯...??
@@ -679,16 +731,16 @@
  워싱턴에서 협상에 나설 예정입니다. </t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>104</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">14일 이스라엘 레바논 협상... 이쪽이 끝나야.....??
 미 이란 협상이 본격적 시작될듯...??
@@ -696,126 +748,126 @@
  워싱턴에서 협상에 나설 예정입니다. </t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" t="n">
         <v>417353348</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026.04.11 20:42</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>백악관-이란자산동결해제 부인.....</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>미국 관리, 이란 자산 동결 해제에 동의했다는 보도를 부인함 - 미국 백악관</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>59</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>백악관-이란자산동결해제 부인..... 미국 관리, 이란 자산 동결 해제에 동의했다는 보도를 부인함 - 미국 백악관</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>417353229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026.04.11 20:42</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>백악관-이란자산동결해제 부인.....</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>미국 관리, 이란 자산 동결 해제에 동의했다는 보도를 부인함 - 미국 백악관</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>59</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>백악관-이란자산동결해제 부인..... 미국 관리, 이란 자산 동결 해제에 동의했다는 보도를 부인함 - 미국 백악관</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>417353229</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2026.04.11 20:18</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>분기매출57조 삼성전자와 삼성증권은 주가가 연...</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">삼성전자와 삼성증권은 주가가 연동된다. 삼전이 잘나가면 삼성증권이 수혜주
 증권주 주도주는 삼성증권 </t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>128</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">분기매출57조 삼성전자와 삼성증권은 주가가 연... 삼성전자와 삼성증권은 주가가 연동된다. 삼전이 잘나가면 삼성증권이 수혜주
 증권주 주도주는 삼성증권 </t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="n">
         <v>417352913</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026.04.11 19:16</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>축하드립니다</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>월요일 슈퍼 떡상</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>21</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>519</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>축하드립니다 월요일 슈퍼 떡상</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>417351998</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026.04.11 19:16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>축하드립니다</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>월요일 슈퍼 떡상</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>21</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>519</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>축하드립니다 월요일 슈퍼 떡상</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>417351998</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>2026.04.11 18:11</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>협상이 향후 주가 하락이냐 ?상승이냐 결정짓을...[1]</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>협의시.... 쭈욱 올라간다~~
 실패시... .쭈욱 내려간다~~
@@ -825,16 +877,16 @@
 -7% =  61,845원 ~</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>188</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>협상이 향후 주가 하락이냐 ?상승이냐 결정짓을...[1] 협의시.... 쭈욱 올라간다~~
 실패시... .쭈욱 내려간다~~
@@ -844,94 +896,94 @@
 -7% =  61,845원 ~</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>417351097</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026.04.11 17:42</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>미래[3]</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>답답할때도 많지만
 이제는 그냥 미래가 좋다~ 
 어떻게 되든간에 오래 같이가자!</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>11</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>158</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>미래[3] 답답할때도 많지만
 이제는 그냥 미래가 좋다~ 
 어떻게 되든간에 오래 같이가자!</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H13" t="n">
         <v>417350770</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026.04.11 16:56</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>협상파토나면[3]</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>6만아래도 진지하게고민스..</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>254</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>협상파토나면[3] 6만아래도 진지하게고민스..</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>417350274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>2026.04.11 16:56</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>협상파토나면[3]</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6만아래도 진지하게고민스..</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>254</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>협상파토나면[3] 6만아래도 진지하게고민스..</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>417350274</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2026.04.11 16:24</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>5대증권사 상승율 비교</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">4월10일 종가기준....
 2월초중순 이슈 찾아 봐라 왜 다른 증권보다 올라는지...
@@ -943,16 +995,16 @@
 삼성증권 ( 50.00 % ) </t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
         <v>332</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">5대증권사 상승율 비교 4월10일 종가기준....
 2월초중순 이슈 찾아 봐라 왜 다른 증권보다 올라는지...
@@ -964,22 +1016,56 @@
 삼성증권 ( 50.00 % ) </t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H15" t="n">
         <v>417349932</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026.04.11 15:39</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>협상 절대로 안됨</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>핵무기 투하가 답이다</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" t="n">
+        <v>84</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>협상 절대로 안됨 핵무기 투하가 답이다</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>417349413</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026.04.11 15:39</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>스페이스 X+xAI IPO 시 3천 조 인정받...[2]</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>[스페이스 X+xAI 3,000조 상장 시]
 최근 시장 보고서를 종합해 볼 때, 스페이스X와 xAI의 상장이 현실화되어 3,000조 원(약 2조 달러)의 기업가치를 인정받는다면 미래에셋증권이 누릴 평가이익은 기존 예상치를 훨씬 상회하는 역대급 수준이 될 것으로 보입니다.
@@ -1015,16 +1101,16 @@
 https://share.google/XOmzQvQ1gPwpumD3V</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D17" t="n">
         <v>23</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E17" t="n">
         <v>5</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F17" t="n">
         <v>608</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>스페이스 X+xAI IPO 시 3천 조 인정받...[2] [스페이스 X+xAI 3,000조 상장 시]
 최근 시장 보고서를 종합해 볼 때, 스페이스X와 xAI의 상장이 현실화되어 3,000조 원(약 2조 달러)의 기업가치를 인정받는다면 미래에셋증권이 누릴 평가이익은 기존 예상치를 훨씬 상회하는 역대급 수준이 될 것으로 보입니다.
@@ -1060,56 +1146,22 @@
 https://share.google/XOmzQvQ1gPwpumD3V</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H17" t="n">
         <v>417349416</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026.04.11 15:39</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>협상 절대로 안됨</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>핵무기 투하가 답이다</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>13</v>
-      </c>
-      <c r="F16" t="n">
-        <v>84</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>협상 절대로 안됨 핵무기 투하가 답이다</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>417349413</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026.04.11 13:40</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>종토방</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>나도  아직 손실이지만
 떨어지면 개잡주
@@ -1117,16 +1169,16 @@
 쫌 느긋하게 갑시다</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>91</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>종토방 나도  아직 손실이지만
 떨어지면 개잡주
@@ -1134,42 +1186,8 @@
 쫌 느긋하게 갑시다</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="H18" t="n">
         <v>417347967</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026.04.11 13:14</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>하방 꽂는 공매도 금지가 시급</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>심각하다고 생각</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>13</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>67</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>하방 꽂는 공매도 금지가 시급 심각하다고 생각</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>417347631</v>
       </c>
     </row>
     <row r="19">
@@ -1180,44 +1198,78 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>미래에셋</t>
+          <t>하방 꽂는 공매도 금지가 시급</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>투자하기 괜찮은듯</t>
+          <t>심각하다고 생각</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>미래에셋 투자하기 괜찮은듯</t>
+          <t>하방 꽂는 공매도 금지가 시급 심각하다고 생각</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>417347622</v>
+        <v>417347631</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>2026.04.11 13:14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>미래에셋</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>투자하기 괜찮은듯</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>19</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>92</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>미래에셋 투자하기 괜찮은듯</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>417347622</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>2026.04.11 12:38</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>어제 움직임은 누가봐도 이상했음[1]</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>항상 지수따라가던넘이 지수랑 반대로움직였다? 것도 코스피지수 1퍼넘게올랐는데??
 이건 먼가 주포의 의도가있는거다ㅋㅋㅋ
@@ -1225,16 +1277,16 @@
 평소랑 다른 비정상적인 흐름이나왔을땐 주식에선 의심해봐야함</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>8</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>5</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>497</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>어제 움직임은 누가봐도 이상했음[1] 항상 지수따라가던넘이 지수랑 반대로움직였다? 것도 코스피지수 1퍼넘게올랐는데??
 이건 먼가 주포의 의도가있는거다ㅋㅋㅋ
@@ -1242,166 +1294,166 @@
 평소랑 다른 비정상적인 흐름이나왔을땐 주식에선 의심해봐야함</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>417347140</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026.04.11 11:49</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>미장 우주항공 관련섹터마감시황</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>무난하게 마감
 즐건주말~</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>6</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>280</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>미장 우주항공 관련섹터마감시황 무난하게 마감
 즐건주말~</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>417346479</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026.04.11 09:38</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>천당,지옥중 하나</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>스페이스x
 부채비율1,015</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>19</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>231</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>천당,지옥중 하나 스페이스x
 부채비율1,015</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>417344566</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026.04.11 08:36</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>이 종목은 난이도 최상급종목이고</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>아무나 수익낼 수 없는 종목인데
 뭐 이리 조무래귀들이 덕지덕지 달라붙어있노?
 다들 개 쳐물려있나?</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D24" t="n">
         <v>6</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>10</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>209</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>이 종목은 난이도 최상급종목이고 아무나 수익낼 수 없는 종목인데
 뭐 이리 조무래귀들이 덕지덕지 달라붙어있노?
 다들 개 쳐물려있나?</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>417343786</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026.04.11 07:43</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>속보&gt;사이더스스페이스+25.45% 폭등!</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>성투.....</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>31</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>446</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>속보&gt;사이더스스페이스+25.45% 폭등! 성투.....</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>417343203</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2026.04.11 07:43</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>속보&gt;사이더스스페이스+25.45% 폭등!</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>성투.....</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>31</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>446</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>속보&gt;사이더스스페이스+25.45% 폭등! 성투.....</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>417343203</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>2026.04.11 07:18</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>어제 분석해준다[1]</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>다른증권주들 달릴때 못감..
 지수와반대로움직임..
@@ -1413,16 +1465,16 @@
 그리고 하나더알려주자면 프로그램이 좀더 비워져야 간다~ 오늘 그래서 프로그램판거임 ㅇㅋ?</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D26" t="n">
         <v>21</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>5</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>953</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>어제 분석해준다[1] 다른증권주들 달릴때 못감..
 지수와반대로움직임..
@@ -1434,22 +1486,22 @@
 그리고 하나더알려주자면 프로그램이 좀더 비워져야 간다~ 오늘 그래서 프로그램판거임 ㅇㅋ?</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>417342972</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026.04.11 07:05</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>기다려라.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>미래에.단타치려구.들어왔나?
 5월말까지 진득하게 기다려라!
@@ -1460,16 +1512,16 @@
 게시판이,지저분하다. 에이~~</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
         <v>17</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>2</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>204</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>기다려라. 미래에.단타치려구.들어왔나?
 5월말까지 진득하게 기다려라!
@@ -1480,56 +1532,56 @@
 게시판이,지저분하다. 에이~~</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>417342845</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026.04.11 03:11</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>시총 36조...[1]</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>아무리 스페이스상장으로 대박쳤다해도 에바지</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>13</v>
-      </c>
-      <c r="F27" t="n">
-        <v>539</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>시총 36조...[1] 아무리 스페이스상장으로 대박쳤다해도 에바지</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>417341600</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>2026.04.11 03:11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>시총 36조...[1]</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>아무리 스페이스상장으로 대박쳤다해도 에바지</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" t="n">
+        <v>539</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>시총 36조...[1] 아무리 스페이스상장으로 대박쳤다해도 에바지</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>417341600</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>2026.04.10 22:32</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>[기술적 분석 가이드] RS · A/D · Ti...[1]</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>오늘은 William O'Neil과 Mark Minervini가 중시한 세 가지 핵심 지표를
 미래에셋증권(006800)에 실제로 적용해 보겠습니다.
@@ -1583,16 +1635,16 @@
 * 본 글은 투자 권유가 아닌 기술적 분석 데이터 공유 목적입니다.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D29" t="n">
         <v>25</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E29" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F29" t="n">
         <v>683</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>[기술적 분석 가이드] RS · A/D · Ti...[1] 오늘은 William O'Neil과 Mark Minervini가 중시한 세 가지 핵심 지표를
 미래에셋증권(006800)에 실제로 적용해 보겠습니다.
@@ -1646,22 +1698,22 @@
 * 본 글은 투자 권유가 아닌 기술적 분석 데이터 공유 목적입니다.</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="H29" t="n">
         <v>417336284</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026.04.10 22:09</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>스페이스X, 작년 영업이익 80억 달러 기록… ...[2]</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>https://www.g-enews.com/article/Global-Biz/2026/01/2026013108050428003bc914ac71_1
 일론 머스크의 우주 탐사 기업 스페이스X가 지난해 약 150억~160억 달러의 매출과 80억 달러(약 11조6000억 원) 규모의 영업이익을 기록했다고 30일(현지시각) 로이터 통신이 소식통들을 인용해 보도했다.
@@ -1671,16 +1723,16 @@
 스페이스X의 가파른 성장세는 위성 인터넷 서비스인 '스타링크(Starlink)'가 주도하고 있다. 소식통들은 스타링크가 전체 매출의 50%에서 최대 80%를 차지하는 핵심 수익원이라고 전했다.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>44</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F30" t="n">
         <v>1080</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>스페이스X, 작년 영업이익 80억 달러 기록… ...[2] https://www.g-enews.com/article/Global-Biz/2026/01/2026013108050428003bc914ac71_1
 일론 머스크의 우주 탐사 기업 스페이스X가 지난해 약 150억~160억 달러의 매출과 80억 달러(약 11조6000억 원) 규모의 영업이익을 기록했다고 30일(현지시각) 로이터 통신이 소식통들을 인용해 보도했다.
@@ -1690,22 +1742,22 @@
 스페이스X의 가파른 성장세는 위성 인터넷 서비스인 '스타링크(Starlink)'가 주도하고 있다. 소식통들은 스타링크가 전체 매출의 50%에서 최대 80%를 차지하는 핵심 수익원이라고 전했다.</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="H30" t="n">
         <v>417335436</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026.04.10 21:15</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>스페이스x[4]</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>25년도 50억달러손실기록
 그래서 외국계증권에서 매도 했구만
@@ -1716,16 +1768,16 @@
 손실원인  xAI  인수와 우주인프라투자</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E31" t="n">
         <v>38</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F31" t="n">
         <v>1253</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>스페이스x[4] 25년도 50억달러손실기록
 그래서 외국계증권에서 매도 했구만
@@ -1736,56 +1788,56 @@
 손실원인  xAI  인수와 우주인프라투자</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="H31" t="n">
         <v>417334282</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026.04.10 20:26</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>아니 뭔 투주야</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일부러 투주 만드나? </t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>7</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>269</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아니 뭔 투주야 일부러 투주 만드나? </t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>417333165</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>2026.04.10 20:26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>아니 뭔 투주야</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일부러 투주 만드나? </t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>269</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아니 뭔 투주야 일부러 투주 만드나? </t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>417333165</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>2026.04.10 19:47</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>스페이스 X 선반영되었다고</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>주절거리면서 전문가가 그랬다고 그러네!!!
 그 전문가는 공매꾼들이것지!!!
@@ -1796,16 +1848,16 @@
 그래!!! 열씨미 해봐라!!!</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D33" t="n">
         <v>29</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E33" t="n">
         <v>1</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>367</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>스페이스 X 선반영되었다고 주절거리면서 전문가가 그랬다고 그러네!!!
 그 전문가는 공매꾼들이것지!!!
@@ -1816,128 +1868,128 @@
 그래!!! 열씨미 해봐라!!!</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="H33" t="n">
         <v>417331979</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026.04.10 19:15</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>미틴 머가 이리빨라~~급보[1]</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>벌써 가동 된다구?</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>20</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>830</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>미틴 머가 이리빨라~~급보[1] 벌써 가동 된다구?</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>417330901</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>2026.04.10 19:15</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>미틴 머가 이리빨라~~급보[1]</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>벌써 가동 된다구?</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>830</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>미틴 머가 이리빨라~~급보[1] 벌써 가동 된다구?</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>417330901</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>2026.04.10 19:13</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>다[1]</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>가는데
 이놈만 왜 안가는거야
 욕 나온다. 스브럴</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D35" t="n">
         <v>26</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E35" t="n">
         <v>2</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F35" t="n">
         <v>297</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>다[1] 가는데
 이놈만 왜 안가는거야
 욕 나온다. 스브럴</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="H35" t="n">
         <v>417330825</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026.04.10 18:42</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>이것들아</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>배당 달달하군아 주식도주고 인생동반주식이다 가즈아!!!!!</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>8</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>160</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>이것들아 배당 달달하군아 주식도주고 인생동반주식이다 가즈아!!!!!</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>417329824</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>2026.04.10 18:42</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>이것들아</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>배당 달달하군아 주식도주고 인생동반주식이다 가즈아!!!!!</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>160</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>이것들아 배당 달달하군아 주식도주고 인생동반주식이다 가즈아!!!!!</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>417329824</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>2026.04.10 18:28</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>공매꾼들 시간은 갔다.[1]</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>아~~처참하고 비굴한 시간
 그 시간의 시작이라면 
@@ -1951,16 +2003,16 @@
 그래!!! 차카게 살자!!!</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>18</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>1</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>243</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>공매꾼들 시간은 갔다.[1] 아~~처참하고 비굴한 시간
 그 시간의 시작이라면 
@@ -1974,90 +2026,90 @@
 그래!!! 차카게 살자!!!</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>417329383</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026.04.10 18:16</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>실적끝[1]</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>이젠 하강시간</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>25</v>
-      </c>
-      <c r="F37" t="n">
-        <v>223</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>실적끝[1] 이젠 하강시간</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>417328950</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026.04.10 18:07</t>
+          <t>2026.04.10 18:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>임원이 매도한거야?[1]</t>
+          <t>실적끝[1]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>똥물튀기누?</t>
+          <t>이젠 하강시간</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>362</v>
+        <v>223</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>임원이 매도한거야?[1] 똥물튀기누?</t>
+          <t>실적끝[1] 이젠 하강시간</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>417328596</v>
+        <v>417328950</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>2026.04.10 18:07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>임원이 매도한거야?[1]</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>똥물튀기누?</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>362</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>임원이 매도한거야?[1] 똥물튀기누?</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>417328596</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>2026.04.10 17:46</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>방탄공견들~~~~~ㅎㄷㄷ</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>공견들 : 우린 방탄공견이야~~여긴 방탄이라구
 갬투주포 : 아직 세방남았다~~
@@ -2065,16 +2117,16 @@
 ㅋㅋㅋㅋ나두 미쳐가는구나ㅋㅋㅋㅋ</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D40" t="n">
         <v>2</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F40" t="n">
         <v>125</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>방탄공견들~~~~~ㅎㄷㄷ 공견들 : 우린 방탄공견이야~~여긴 방탄이라구
 갬투주포 : 아직 세방남았다~~
@@ -2082,22 +2134,22 @@
 ㅋㅋㅋㅋ나두 미쳐가는구나ㅋㅋㅋㅋ</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="H40" t="n">
         <v>417327724</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>2026.04.10 17:42</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>다시한번말하지만[1]</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>이런종목은 걍 옆으로 기간횡보할때 모아가는거다
 어느날갑자기 전날새벽이나 장전에 뉴스떠서 갭 10퍼떠서 시작하면 못잡는거임ㅋㅋㅋㅋ
@@ -2106,16 +2158,16 @@
 지금 일정 가까이 남아있는게 스페이스x말고 머있음?</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D41" t="n">
         <v>28</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E41" t="n">
         <v>1</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>690</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>다시한번말하지만[1] 이런종목은 걍 옆으로 기간횡보할때 모아가는거다
 어느날갑자기 전날새벽이나 장전에 뉴스떠서 갭 10퍼떠서 시작하면 못잡는거임ㅋㅋㅋㅋ
@@ -2124,274 +2176,274 @@
 지금 일정 가까이 남아있는게 스페이스x말고 머있음?</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="H41" t="n">
         <v>417327533</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026.04.10 17:21</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>공매도[1]</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>비율 높은 이유는 증권주가 경기에 민감하기에..앞으로 떨어질것을 예상해서임.. 공매도 비중 높을때는 매수에 신중해야는데 ..생각없이 오늘 많이 매수해버렸네....</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>10</v>
-      </c>
-      <c r="F41" t="n">
-        <v>272</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>공매도[1] 비율 높은 이유는 증권주가 경기에 민감하기에..앞으로 떨어질것을 예상해서임.. 공매도 비중 높을때는 매수에 신중해야는데 ..생각없이 오늘 많이 매수해버렸네....</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>417326503</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026.04.10 17:20</t>
+          <t>2026.04.10 17:21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>오늘[2]</t>
+          <t>공매도[1]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">67000이 싸다구 생각해서 매수 했는뎨  매수하자마자  손실  이네요  큰손싵은  이니어서  가져가요 에프터 종가에  물타기 대기 </t>
+          <t>비율 높은 이유는 증권주가 경기에 민감하기에..앞으로 떨어질것을 예상해서임.. 공매도 비중 높을때는 매수에 신중해야는데 ..생각없이 오늘 많이 매수해버렸네....</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>389</v>
+        <v>272</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">오늘[2] 67000이 싸다구 생각해서 매수 했는뎨  매수하자마자  손실  이네요  큰손싵은  이니어서  가져가요 에프터 종가에  물타기 대기 </t>
+          <t>공매도[1] 비율 높은 이유는 증권주가 경기에 민감하기에..앞으로 떨어질것을 예상해서임.. 공매도 비중 높을때는 매수에 신중해야는데 ..생각없이 오늘 많이 매수해버렸네....</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>417326482</v>
+        <v>417326503</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026.04.10 17:20</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>오늘[2]</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67000이 싸다구 생각해서 매수 했는뎨  매수하자마자  손실  이네요  큰손싵은  이니어서  가져가요 에프터 종가에  물타기 대기 </t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>389</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오늘[2] 67000이 싸다구 생각해서 매수 했는뎨  매수하자마자  손실  이네요  큰손싵은  이니어서  가져가요 에프터 종가에  물타기 대기 </t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>417326482</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>2026.04.10 17:17</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>기레기들</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>공매도와 한편인걸 다안다....장중에 공매도
 실큰치고. 넥스트장에 뉴스내야지....그래야
 기레기밥값하지 ...</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D44" t="n">
         <v>2</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>1</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F44" t="n">
         <v>111</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>기레기들 공매도와 한편인걸 다안다....장중에 공매도
 실큰치고. 넥스트장에 뉴스내야지....그래야
 기레기밥값하지 ...</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="H44" t="n">
         <v>417326323</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>2026.04.10 17:17</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>X corp에 3000억  스페이스엑스에  2000[1]</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>X ai에 1000억
 합 6천억
 200배는 잡아야되는거 맞지?</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D45" t="n">
         <v>18</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E45" t="n">
         <v>1</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F45" t="n">
         <v>360</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>X corp에 3000억  스페이스엑스에  2000[1] X ai에 1000억
 합 6천억
 200배는 잡아야되는거 맞지?</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="H45" t="n">
         <v>417326319</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2026.04.10 17:14</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>머스크 X 그룹에 6천억 태웠네 ㄷㄷㄷㄷ[1]</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>지금 가치가 200배는 뛰었을건데
 120조원??  ㄷㄷㄷㄷㄷ</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D46" t="n">
         <v>16</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E46" t="n">
         <v>2</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F46" t="n">
         <v>388</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>머스크 X 그룹에 6천억 태웠네 ㄷㄷㄷㄷ[1] 지금 가치가 200배는 뛰었을건데
 120조원??  ㄷㄷㄷㄷㄷ</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="H46" t="n">
         <v>417326207</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026.04.10 17:04</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>참</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>해도해도  너무하구만  2개윌을 박스안에 가둬놓고  오도가도 못하게ㅣ 하네  도대체 어떤ㄴ 들일까</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>15</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>122</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>참 해도해도  너무하구만  2개윌을 박스안에 가둬놓고  오도가도 못하게ㅣ 하네  도대체 어떤ㄴ 들일까</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>417325629</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>2026.04.10 17:04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>참</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>해도해도  너무하구만  2개윌을 박스안에 가둬놓고  오도가도 못하게ㅣ 하네  도대체 어떤ㄴ 들일까</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>122</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>참 해도해도  너무하구만  2개윌을 박스안에 가둬놓고  오도가도 못하게ㅣ 하네  도대체 어떤ㄴ 들일까</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>417325629</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>2026.04.10 17:02</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>꼬라지보니까 공매도가 진짜 적폐다[3]</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>순기능은 개뿔ㅋㅋㅋ
 장초에 오르는거 처박고
 중간에 오를만하면 끌어내리고</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D48" t="n">
         <v>21</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E48" t="n">
         <v>1</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>214</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>꼬라지보니까 공매도가 진짜 적폐다[3] 순기능은 개뿔ㅋㅋㅋ
 장초에 오르는거 처박고
 중간에 오를만하면 끌어내리고</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="H48" t="n">
         <v>417325547</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>2026.04.10 17:00</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>이것도 증권계의 개잡주...[2]</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>어떻게 나는 사는 족족 
 개잡주만 걸리나...
@@ -2401,16 +2453,16 @@
 역대급 개잡주...인정..</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D49" t="n">
         <v>15</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E49" t="n">
         <v>2</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F49" t="n">
         <v>208</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>이것도 증권계의 개잡주...[2] 어떻게 나는 사는 족족 
 개잡주만 걸리나...
@@ -2420,826 +2472,826 @@
 역대급 개잡주...인정..</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="H49" t="n">
         <v>417325449</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>2026.04.10 16:56</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>와 방금 분석글썼는데 누가지웠냐</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>세력이지웠냐?ㅋㅋㅋㅋ
 딱걸렸지? 소름돋는다</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D50" t="n">
         <v>0</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F50" t="n">
         <v>120</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>와 방금 분석글썼는데 누가지웠냐 세력이지웠냐?ㅋㅋㅋㅋ
 딱걸렸지? 소름돋는다</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="H50" t="n">
         <v>417325246</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026.04.10 16:55</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>공매 친 이유가 있을낀데</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>11%나? 와 씨 뒤지겠네</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>8</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>112</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>공매 친 이유가 있을낀데 11%나? 와 씨 뒤지겠네</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>417325198</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026.04.10 16:44</t>
+          <t>2026.04.10 16:55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>스페이스x 손실임?[1]</t>
+          <t>공매 친 이유가 있을낀데</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>손실뉴스나오네</t>
+          <t>11%나? 와 씨 뒤지겠네</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>616</v>
+        <v>112</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>스페이스x 손실임?[1] 손실뉴스나오네</t>
+          <t>공매 친 이유가 있을낀데 11%나? 와 씨 뒤지겠네</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>417324598</v>
+        <v>417325198</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026.04.10 16:42</t>
+          <t>2026.04.10 16:44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>너무 오르긴 했네;</t>
+          <t>스페이스x 손실임?[1]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ㅋㅌㅌㅌㅌㅌㅌ</t>
+          <t>손실뉴스나오네</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F52" t="n">
-        <v>90</v>
+        <v>616</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>너무 오르긴 했네; ㅋㅌㅌㅌㅌㅌㅌ</t>
+          <t>스페이스x 손실임?[1] 손실뉴스나오네</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>417324486</v>
+        <v>417324598</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026.04.10 16:30</t>
+          <t>2026.04.10 16:42</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>스페이스x랑 뭐있는데 뭐해?</t>
+          <t>너무 오르긴 했네;</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>집팔고 땅팔고 차팔고 매수해~ 강원랜드가서 바카라나 돌리자구~</t>
+          <t>ㅋㅌㅌㅌㅌㅌㅌ</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F53" t="n">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>스페이스x랑 뭐있는데 뭐해? 집팔고 땅팔고 차팔고 매수해~ 강원랜드가서 바카라나 돌리자구~</t>
+          <t>너무 오르긴 했네; ㅋㅌㅌㅌㅌㅌㅌ</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>417323726</v>
+        <v>417324486</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>2026.04.10 16:30</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>스페이스x랑 뭐있는데 뭐해?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>집팔고 땅팔고 차팔고 매수해~ 강원랜드가서 바카라나 돌리자구~</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>16</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>131</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>스페이스x랑 뭐있는데 뭐해? 집팔고 땅팔고 차팔고 매수해~ 강원랜드가서 바카라나 돌리자구~</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>417323726</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>2026.04.10 16:22</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>개인적으로 공매도 세력은</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>그 누가 됐던간에 아예 박살이 나서 항상 패배했으면 좋겠음
 -끝-</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D55" t="n">
         <v>25</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E55" t="n">
         <v>2</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F55" t="n">
         <v>111</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>개인적으로 공매도 세력은 그 누가 됐던간에 아예 박살이 나서 항상 패배했으면 좋겠음
 -끝-</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>417323219</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026.04.10 16:22</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>최근 스페이스X 상장 추정 가치로 따지면</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3월 주총에서 평가한 1조 8천억보다 9천억에서 1.3조 더 많이 나오는데 주가는 지지부진이네요. </t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>19</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>217</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최근 스페이스X 상장 추정 가치로 따지면 3월 주총에서 평가한 1조 8천억보다 9천억에서 1.3조 더 많이 나오는데 주가는 지지부진이네요. </t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>417323208</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>2026.04.10 16:22</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>최근 스페이스X 상장 추정 가치로 따지면</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3월 주총에서 평가한 1조 8천억보다 9천억에서 1.3조 더 많이 나오는데 주가는 지지부진이네요. </t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>19</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>217</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최근 스페이스X 상장 추정 가치로 따지면 3월 주총에서 평가한 1조 8천억보다 9천억에서 1.3조 더 많이 나오는데 주가는 지지부진이네요. </t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>417323208</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>2026.04.10 16:18</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>얘는 스윙종목임[1]</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>스페이스x상장까지 진득히 끌고갈 종목임
 단타치는종목이아님 ㅇㅋ?</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D57" t="n">
         <v>21</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F57" t="n">
         <v>305</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>얘는 스윙종목임[1] 스페이스x상장까지 진득히 끌고갈 종목임
 단타치는종목이아님 ㅇㅋ?</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="H57" t="n">
         <v>417322965</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026.04.10 16:09</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>공매도 11%ㅋㅋㅋㅋㅋㅋ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>못올라가는 이유가 있구만..</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>16</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>149</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>공매도 11%ㅋㅋㅋㅋㅋㅋ 못올라가는 이유가 있구만..</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>417322297</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>2026.04.10 16:09</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>공매도 11%ㅋㅋㅋㅋㅋㅋ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>못올라가는 이유가 있구만..</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>16</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>149</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>공매도 11%ㅋㅋㅋㅋㅋㅋ 못올라가는 이유가 있구만..</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>417322297</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>2026.04.10 15:59</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>종가</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>666 마음에 안드네.
 악마의 숫자네ㅋㅋㅋㅋㅋ</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D59" t="n">
         <v>7</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E59" t="n">
         <v>2</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F59" t="n">
         <v>82</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>종가 666 마음에 안드네.
 악마의 숫자네ㅋㅋㅋㅋㅋ</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="H59" t="n">
         <v>417321558</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026.04.10 15:55</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>월요 일 엔 분명</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋은 가격  받을것 </t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>20</v>
-      </c>
-      <c r="E59" t="n">
-        <v>5</v>
-      </c>
-      <c r="F59" t="n">
-        <v>134</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">월요 일 엔 분명 좋은 가격  받을것 </t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>417321232</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026.04.10 15:39</t>
+          <t>2026.04.10 15:55</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>엇!!!정신못차리고 오늘 또 공견들 러쉬했네~~</t>
+          <t>월요 일 엔 분명</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>자~~~공견풀코스 식사준비 좀 해보자~~~캬캬</t>
+          <t xml:space="preserve">좋은 가격  받을것 </t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F60" t="n">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>엇!!!정신못차리고 오늘 또 공견들 러쉬했네~~ 자~~~공견풀코스 식사준비 좀 해보자~~~캬캬</t>
+          <t xml:space="preserve">월요 일 엔 분명 좋은 가격  받을것 </t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>417319645</v>
+        <v>417321232</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>2026.04.10 15:39</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>엇!!!정신못차리고 오늘 또 공견들 러쉬했네~~</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>자~~~공견풀코스 식사준비 좀 해보자~~~캬캬</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>111</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>엇!!!정신못차리고 오늘 또 공견들 러쉬했네~~ 자~~~공견풀코스 식사준비 좀 해보자~~~캬캬</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>417319645</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>2026.04.10 15:35</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>이건 증권주가 아니고</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>개잡준가 보군 오늘
 혼자 죽쑤네 ㅎ 배당도 개판이더니!</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D62" t="n">
         <v>8</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E62" t="n">
         <v>3</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F62" t="n">
         <v>126</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>이건 증권주가 아니고 개잡준가 보군 오늘
 혼자 죽쑤네 ㅎ 배당도 개판이더니!</t>
         </is>
       </c>
-      <c r="H61" t="n">
+      <c r="H62" t="n">
         <v>417319259</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026.04.10 15:32</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>7만 가려면 한세월~[1]</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>기대하지마 노노노 스페이스 X 보고왔제? ㅋㅋ이미반영끝~</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>5</v>
-      </c>
-      <c r="E62" t="n">
-        <v>9</v>
-      </c>
-      <c r="F62" t="n">
-        <v>223</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>7만 가려면 한세월~[1] 기대하지마 노노노 스페이스 X 보고왔제? ㅋㅋ이미반영끝~</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>417318770</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026.04.10 15:29</t>
+          <t>2026.04.10 15:32</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>이거</t>
+          <t>7만 가려면 한세월~[1]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>맛 탱이 갔네 ㅋ</t>
+          <t>기대하지마 노노노 스페이스 X 보고왔제? ㅋㅋ이미반영끝~</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>71</v>
+        <v>223</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>이거 맛 탱이 갔네 ㅋ</t>
+          <t>7만 가려면 한세월~[1] 기대하지마 노노노 스페이스 X 보고왔제? ㅋㅋ이미반영끝~</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>417318472</v>
+        <v>417318770</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026.04.10 15:19</t>
+          <t>2026.04.10 15:29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>져.....졌다~~~~오늘은 졌다...</t>
+          <t>이거</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>다음주를 기약하마~~~큭 ㅜㅜ</t>
+          <t>맛 탱이 갔네 ㅋ</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>져.....졌다~~~~오늘은 졌다... 다음주를 기약하마~~~큭 ㅜㅜ</t>
+          <t>이거 맛 탱이 갔네 ㅋ</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>417317115</v>
+        <v>417318472</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>2026.04.10 15:19</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>져.....졌다~~~~오늘은 졌다...</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>다음주를 기약하마~~~큭 ㅜㅜ</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" t="n">
+        <v>81</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>져.....졌다~~~~오늘은 졌다... 다음주를 기약하마~~~큭 ㅜㅜ</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>417317115</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>2026.04.10 15:16</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>뭐지?야는?[1]</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>딴 증권주는 다 오르는데 미래는 왜? 
 이럴까요?</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D66" t="n">
         <v>12</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E66" t="n">
         <v>0</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F66" t="n">
         <v>160</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>뭐지?야는?[1] 딴 증권주는 다 오르는데 미래는 왜? 
 이럴까요?</t>
         </is>
       </c>
-      <c r="H65" t="n">
+      <c r="H66" t="n">
         <v>417316645</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>2026.04.10 15:10</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>혼자 빌빌대냐...[1]</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>정체가 뭐냐
 스페이스x하고 정말 관계 있는거 맞냐??</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D67" t="n">
         <v>12</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E67" t="n">
         <v>0</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F67" t="n">
         <v>119</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>혼자 빌빌대냐...[1] 정체가 뭐냐
 스페이스x하고 정말 관계 있는거 맞냐??</t>
         </is>
       </c>
-      <c r="H66" t="n">
+      <c r="H67" t="n">
         <v>417315771</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>2026.04.10 15:08</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>형들 이거 진짜 오를까? 갖고있으면 되는걸...[3]</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>664층...
 어머니가 지인들 말만 듣고 산 대우건설 
 그제 상한가 치는거 보니까 현타가 오네</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D68" t="n">
         <v>12</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E68" t="n">
         <v>1</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F68" t="n">
         <v>453</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>형들 이거 진짜 오를까? 갖고있으면 되는걸...[3] 664층...
 어머니가 지인들 말만 듣고 산 대우건설 
 그제 상한가 치는거 보니까 현타가 오네</t>
         </is>
       </c>
-      <c r="H67" t="n">
+      <c r="H68" t="n">
         <v>417315484</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026.04.10 14:59</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>하루 종일</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>삽질하네 1분기 실적 좋다는데 뭐하는거야?</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>16</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>95</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>하루 종일 삽질하네 1분기 실적 좋다는데 뭐하는거야?</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>417314289</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026.04.10 14:53</t>
+          <t>2026.04.10 14:59</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>일부러 쳐누르네[1]</t>
+          <t>하루 종일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>다보임ㅋㅋㅋㅋ</t>
+          <t>삽질하네 1분기 실적 좋다는데 뭐하는거야?</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>일부러 쳐누르네[1] 다보임ㅋㅋㅋㅋ</t>
+          <t>하루 종일 삽질하네 1분기 실적 좋다는데 뭐하는거야?</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>417313538</v>
+        <v>417314289</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>2026.04.10 14:53</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>일부러 쳐누르네[1]</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>다보임ㅋㅋㅋㅋ</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>17</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>237</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>일부러 쳐누르네[1] 다보임ㅋㅋㅋㅋ</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>417313538</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>2026.04.10 14:42</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>65에서 계속 빙빙 돈다고 했냐 안했냐? ...[3]</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>지금 엄청 간보는 겨 ㅋㅋㅋㅋ
 내가 말했자녀. 여기가 꼭지점이라고 ㅋㅋㅋ
 근데 아직도 7만원 기다리는겨? ㅋㅋ</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D71" t="n">
         <v>0</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E71" t="n">
         <v>15</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F71" t="n">
         <v>357</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>65에서 계속 빙빙 돈다고 했냐 안했냐? ...[3] 지금 엄청 간보는 겨 ㅋㅋㅋㅋ
 내가 말했자녀. 여기가 꼭지점이라고 ㅋㅋㅋ
 근데 아직도 7만원 기다리는겨? ㅋㅋ</t>
         </is>
       </c>
-      <c r="H70" t="n">
+      <c r="H71" t="n">
         <v>417312122</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026.04.10 14:36</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>어떤. ㅆ.    가[1]</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>자꾸  파는가</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>8</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>171</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>어떤. ㅆ.    가[1] 자꾸  파는가</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>417311390</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>2026.04.10 14:36</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>어떤. ㅆ.    가[1]</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>자꾸  파는가</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>171</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>어떤. ㅆ.    가[1] 자꾸  파는가</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>417311390</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>2026.04.10 14:35</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>세력들이 흔하게 쓰는 수법[2]</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>장기간 횡보로 개미들을 지루하게 만드는것.
 다른주들은 날아다니는데 내가 산 주식들은
@@ -3250,16 +3302,16 @@
 미증는 악재가 없으니 끝까지 버티시길...</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D73" t="n">
         <v>32</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E73" t="n">
         <v>0</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F73" t="n">
         <v>603</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>세력들이 흔하게 쓰는 수법[2] 장기간 횡보로 개미들을 지루하게 만드는것.
 다른주들은 날아다니는데 내가 산 주식들은
@@ -3270,90 +3322,90 @@
 미증는 악재가 없으니 끝까지 버티시길...</t>
         </is>
       </c>
-      <c r="H72" t="n">
+      <c r="H73" t="n">
         <v>417311253</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026.04.10 14:28</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>오늘 배당금 들어왓다</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>스페이스 X</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>7</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="n">
-        <v>284</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>오늘 배당금 들어왓다 스페이스 X</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>417310335</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026.04.10 14:21</t>
+          <t>2026.04.10 14:28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>스페이스엑스 보고 들어가 ?[1]</t>
+          <t>오늘 배당금 들어왓다</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">지금 매수 기회 맞냐 ? </t>
+          <t>스페이스 X</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>553</v>
+        <v>284</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">스페이스엑스 보고 들어가 ?[1] 지금 매수 기회 맞냐 ? </t>
+          <t>오늘 배당금 들어왓다 스페이스 X</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>417309429</v>
+        <v>417310335</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>2026.04.10 14:21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>스페이스엑스 보고 들어가 ?[1]</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지금 매수 기회 맞냐 ? </t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>553</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스페이스엑스 보고 들어가 ?[1] 지금 매수 기회 맞냐 ? </t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>417309429</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>2026.04.10 14:16</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>날은 받아 놓았다.[2]</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t xml:space="preserve">스페이스X 상장땐 미래에셋증권 ‘초대박’
 박*경 기자 입력2026.04.10. 오전 11:42
@@ -3383,16 +3435,16 @@
   </t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D76" t="n">
         <v>13</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E76" t="n">
         <v>1</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F76" t="n">
         <v>563</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">날은 받아 놓았다.[2] 스페이스X 상장땐 미래에셋증권 ‘초대박’
 박*경 기자 입력2026.04.10. 오전 11:42
@@ -3422,56 +3474,56 @@
   </t>
         </is>
       </c>
-      <c r="H75" t="n">
+      <c r="H76" t="n">
         <v>417308771</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026.04.10 14:12</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>고...고마해라....마이 눌렀다 아이가~...</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>그라다 골로간다잉~~~</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>13</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>90</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>고...고마해라....마이 눌렀다 아이가~... 그라다 골로간다잉~~~</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>417308357</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>2026.04.10 14:12</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>고...고마해라....마이 눌렀다 아이가~...</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>그라다 골로간다잉~~~</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>13</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>90</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>고...고마해라....마이 눌렀다 아이가~... 그라다 골로간다잉~~~</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>417308357</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>2026.04.10 14:10</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>공매도가 많은 주식…</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>공매도 많은 탑3 
 엘지에너지 현대차 한미반도체..
@@ -3481,16 +3533,16 @@
 자신없으면 털고나가라...</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D78" t="n">
         <v>16</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E78" t="n">
         <v>0</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F78" t="n">
         <v>308</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>공매도가 많은 주식… 공매도 많은 탑3 
 엘지에너지 현대차 한미반도체..
@@ -3500,232 +3552,232 @@
 자신없으면 털고나가라...</t>
         </is>
       </c>
-      <c r="H77" t="n">
+      <c r="H78" t="n">
         <v>417308100</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026.04.10 14:03</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>박스 2달 쳤다!!!</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>움직임이 두에빌인데??</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>8</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>118</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>박스 2달 쳤다!!! 움직임이 두에빌인데??</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>417307279</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026.04.10 14:00</t>
+          <t>2026.04.10 14:03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>오후도 똑같누</t>
+          <t>박스 2달 쳤다!!!</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>7만은 절대못넘겟다 이번달은</t>
+          <t>움직임이 두에빌인데??</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>오후도 똑같누 7만은 절대못넘겟다 이번달은</t>
+          <t>박스 2달 쳤다!!! 움직임이 두에빌인데??</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>417306945</v>
+        <v>417307279</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026.04.10 13:58</t>
+          <t>2026.04.10 14:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>공매도척결.</t>
+          <t>오후도 똑같누</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>다 팔고 갑니다.</t>
+          <t>7만은 절대못넘겟다 이번달은</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>공매도척결. 다 팔고 갑니다.</t>
+          <t>오후도 똑같누 7만은 절대못넘겟다 이번달은</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>417306731</v>
+        <v>417306945</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026.04.10 13:49</t>
+          <t>2026.04.10 13:58</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>더 떨궈야 가려나..</t>
+          <t>공매도척결.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>아님 뭘까..</t>
+          <t>다 팔고 갑니다.</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>더 떨궈야 가려나.. 아님 뭘까..</t>
+          <t>공매도척결. 다 팔고 갑니다.</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>417305740</v>
+        <v>417306731</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>2026.04.10 13:49</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>더 떨궈야 가려나..</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>아님 뭘까..</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>61</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>더 떨궈야 가려나.. 아님 뭘까..</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>417305740</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>2026.04.10 13:45</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>얘는 증권 1위 회사가 대체 머하냐</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>증권주들 다 날라다니는데 1위회사가 지혼자 죽쓰고 앉았노
 스페이스 기사만 뜨면 폭등하고 아니면 그냥 어영부영 시간만 때우네
 이래가지고 6월까지 10만원 가겠냐 정신차려라 미에증아</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D83" t="n">
         <v>8</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E83" t="n">
         <v>1</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F83" t="n">
         <v>166</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>얘는 증권 1위 회사가 대체 머하냐 증권주들 다 날라다니는데 1위회사가 지혼자 죽쓰고 앉았노
 스페이스 기사만 뜨면 폭등하고 아니면 그냥 어영부영 시간만 때우네
 이래가지고 6월까지 10만원 가겠냐 정신차려라 미에증아</t>
         </is>
       </c>
-      <c r="H82" t="n">
+      <c r="H83" t="n">
         <v>417305288</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>2026.04.10 13:41</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>잘버티고 힘모아서 다음 주 날라가자</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>주말에 종전했다고 뉴스 나오겠지
 다음주 월요일 전종목 폭등하자</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D84" t="n">
         <v>14</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E84" t="n">
         <v>0</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F84" t="n">
         <v>69</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>잘버티고 힘모아서 다음 주 날라가자 주말에 종전했다고 뉴스 나오겠지
 다음주 월요일 전종목 폭등하자</t>
         </is>
       </c>
-      <c r="H83" t="n">
+      <c r="H84" t="n">
         <v>417304853</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>2026.04.10 13:37</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>공매도 세력[1]</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>징글 징글하다
 전체상장주중에서  4위 기록
@@ -3734,16 +3786,16 @@
 언젠가는 박살나겠지</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D85" t="n">
         <v>15</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E85" t="n">
         <v>0</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F85" t="n">
         <v>191</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>공매도 세력[1] 징글 징글하다
 전체상장주중에서  4위 기록
@@ -3752,180 +3804,146 @@
 언젠가는 박살나겠지</t>
         </is>
       </c>
-      <c r="H84" t="n">
+      <c r="H85" t="n">
         <v>417304305</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026.04.10 13:31</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>난 돈벌준비 되었어[2]</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>이제 쳐 올리도록</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>252</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>난 돈벌준비 되었어[2] 이제 쳐 올리도록</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>417303593</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026.04.10 13:30</t>
+          <t>2026.04.10 13:31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>일봉20선이 수평으로</t>
+          <t>난 돈벌준비 되었어[2]</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>펴질때 간다..</t>
+          <t>이제 쳐 올리도록</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>일봉20선이 수평으로 펴질때 간다..</t>
+          <t>난 돈벌준비 되었어[2] 이제 쳐 올리도록</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>417303472</v>
+        <v>417303593</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026.04.10 13:28</t>
+          <t>2026.04.10 13:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>일봉20선이 수평으로</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>스페이스X 대장주는 여기아닌가</t>
+          <t>펴질때 간다..</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>. 스페이스X 대장주는 여기아닌가</t>
+          <t>일봉20선이 수평으로 펴질때 간다..</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>417303112</v>
+        <v>417303472</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>2026.04.10 13:28</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>스페이스X 대장주는 여기아닌가</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>34</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>. 스페이스X 대장주는 여기아닌가</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>417303112</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>2026.04.10 13:25</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>삼전 이어 SK하이닉스·미래에셋證도 '슈퍼 실...[2]</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>삼전, 하이닉스, 미래에셋증권 !!!
 미래에셋증권 1분기 예상치보다 7,680억원 초과달성 !!!</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D89" t="n">
         <v>9</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E89" t="n">
         <v>0</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F89" t="n">
         <v>353</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>삼전 이어 SK하이닉스·미래에셋證도 '슈퍼 실...[2] 삼전, 하이닉스, 미래에셋증권 !!!
 미래에셋증권 1분기 예상치보다 7,680억원 초과달성 !!!</t>
         </is>
       </c>
-      <c r="H88" t="n">
+      <c r="H89" t="n">
         <v>417302771</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026.04.10 13:20</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>보합에 갔다놓는다..90%</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" t="n">
-        <v>69</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>종가 보합에 갔다놓는다..90%</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>417302154</v>
       </c>
     </row>
     <row r="90">
@@ -3936,342 +3954,340 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>야는</t>
+          <t>종가</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>아직도 몸 풀고 있냐...</t>
+          <t>보합에 갔다놓는다..90%</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>야는 아직도 몸 풀고 있냐...</t>
+          <t>종가 보합에 갔다놓는다..90%</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>417302101</v>
+        <v>417302154</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026.04.10 13:15</t>
+          <t>2026.04.10 13:20</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>외</t>
+          <t>야는</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>사서 떨구는 작전이냐 ㅈㄱㄹ</t>
+          <t>아직도 몸 풀고 있냐...</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>외 사서 떨구는 작전이냐 ㅈㄱㄹ</t>
+          <t>야는 아직도 몸 풀고 있냐...</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>417301624</v>
+        <v>417302101</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>2026.04.10 13:15</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>외</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>사서 떨구는 작전이냐 ㅈㄱㄹ</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>38</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>외 사서 떨구는 작전이냐 ㅈㄱㄹ</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>417301624</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>2026.04.10 13:09</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>우리 미에증[1]</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t xml:space="preserve">머리 빵구나겠다
 그만좀 때려... </t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D93" t="n">
         <v>7</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E93" t="n">
         <v>0</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F93" t="n">
         <v>116</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">우리 미에증[1] 머리 빵구나겠다
 그만좀 때려... </t>
         </is>
       </c>
-      <c r="H92" t="n">
+      <c r="H93" t="n">
         <v>417300846</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026.04.10 13:00</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>다른 증권주 다 오르는데</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>혼자 음전인 건  좀 용서가 안된다^^</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>12</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>119</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>다른 증권주 다 오르는데 혼자 음전인 건  좀 용서가 안된다^^</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>417299784</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>2026.04.10 13:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>다른 증권주 다 오르는데</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>혼자 음전인 건  좀 용서가 안된다^^</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>119</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>다른 증권주 다 오르는데 혼자 음전인 건  좀 용서가 안된다^^</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>417299784</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>2026.04.10 12:51</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>코스피 6000넘으면 다시가고</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>6500가면 7만중반
 7000가야 8~9만간다</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D95" t="n">
         <v>0</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E95" t="n">
         <v>6</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F95" t="n">
         <v>103</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>코스피 6000넘으면 다시가고 6500가면 7만중반
 7000가야 8~9만간다</t>
         </is>
       </c>
-      <c r="H94" t="n">
+      <c r="H95" t="n">
         <v>417298715</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026.04.10 12:48</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>아직도믿어? ㅋㅋㅋㅋ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>단타칠거면 여기집말고다른집찾어~ 오후도 똑같혀</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>2</v>
-      </c>
-      <c r="E95" t="n">
-        <v>3</v>
-      </c>
-      <c r="F95" t="n">
-        <v>115</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>아직도믿어? ㅋㅋㅋㅋ 단타칠거면 여기집말고다른집찾어~ 오후도 똑같혀</t>
-        </is>
-      </c>
-      <c r="H95" t="n">
-        <v>417298302</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026.04.10 12:45</t>
+          <t>2026.04.10 12:48</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>배당</t>
+          <t>아직도믿어? ㅋㅋㅋㅋ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>고수님들,배당고지서를 받았는데 미래에셋주식으로 주는 것은 세금은 어떻게 되나요?</t>
+          <t>단타칠거면 여기집말고다른집찾어~ 오후도 똑같혀</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>배당 고수님들,배당고지서를 받았는데 미래에셋주식으로 주는 것은 세금은 어떻게 되나요?</t>
+          <t>아직도믿어? ㅋㅋㅋㅋ 단타칠거면 여기집말고다른집찾어~ 오후도 똑같혀</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>417297984</v>
+        <v>417298302</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026.04.10 12:43</t>
+          <t>2026.04.10 12:45</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>다 탈출</t>
+          <t>배당</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>개뻥인 갑다!</t>
+          <t>고수님들,배당고지서를 받았는데 미래에셋주식으로 주는 것은 세금은 어떻게 되나요?</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>다 탈출 개뻥인 갑다!</t>
+          <t>배당 고수님들,배당고지서를 받았는데 미래에셋주식으로 주는 것은 세금은 어떻게 되나요?</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>417297677</v>
+        <v>417297984</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026.04.10 12:40</t>
+          <t>2026.04.10 12:43</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>벤처투자의</t>
+          <t>다 탈출</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>어쩌다가 꼬봉이 됐나</t>
+          <t>개뻥인 갑다!</t>
         </is>
       </c>
       <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
         <v>3</v>
       </c>
-      <c r="E98" t="n">
-        <v>2</v>
-      </c>
       <c r="F98" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>벤처투자의 어쩌다가 꼬봉이 됐나</t>
+          <t>다 탈출 개뻥인 갑다!</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>417297249</v>
+        <v>417297677</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026.04.10 12:38</t>
+          <t>2026.04.10 12:40</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6월  기대!</t>
+          <t>벤처투자의</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>미래 는 6윌달 가야 오르나?
-지글지글 !</t>
+          <t>어쩌다가 꼬봉이 됐나</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
         <v>79</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>6월  기대! 미래 는 6윌달 가야 오르나?
-지글지글 !</t>
+          <t>벤처투자의 어쩌다가 꼬봉이 됐나</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>417297051</v>
+        <v>417297249</v>
       </c>
     </row>
     <row r="100">
@@ -4682,48 +4698,10 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>참고하나해주면[2]</t>
+          <t>버핏은 코카콜라를 매수한다 음료수주 대박주  ...</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
-        <is>
-          <t>얘가 오늘 못가고있지?
-만약 주말사이에 글로벌악재뉴스떠서 월욜 하락장나오면말이다
-이놈은 오늘 못올랐기때매 월욜에 덜빠지거나 안빠질수있다~ ㅇㅋ?</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" t="n">
-        <v>2</v>
-      </c>
-      <c r="F111" t="n">
-        <v>183</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>참고하나해주면[2] 얘가 오늘 못가고있지?
-만약 주말사이에 글로벌악재뉴스떠서 월욜 하락장나오면말이다
-이놈은 오늘 못올랐기때매 월욜에 덜빠지거나 안빠질수있다~ ㅇㅋ?</t>
-        </is>
-      </c>
-      <c r="H111" t="n">
-        <v>417293168</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026.04.10 12:07</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>버핏은 코카콜라를 매수한다 음료수주 대박주  ...</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
         <is>
           <t>버핏은 코카콜라를 매수한다 음료수주 대박주 
 미국 빙그레 바나나맛우유 판매급증 대박 빙그레 주식투자해서 버핏되자 코카콜라처럼
@@ -4739,16 +4717,16 @@
 빙그레는 이 같은 성장세를 기반으로 북미 공략을 한층 강화할 계획이다. 현지 유통망을 추가로 확대하고, 다양한 맛과 제품군을 통해 소비자 접점을 넓힌다는 전략이다.</t>
         </is>
       </c>
-      <c r="D112" t="n">
+      <c r="D111" t="n">
         <v>0</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E111" t="n">
         <v>0</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F111" t="n">
         <v>84</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>버핏은 코카콜라를 매수한다 음료수주 대박주  ... 버핏은 코카콜라를 매수한다 음료수주 대박주 
 미국 빙그레 바나나맛우유 판매급증 대박 빙그레 주식투자해서 버핏되자 코카콜라처럼
@@ -4764,8 +4742,46 @@
 빙그레는 이 같은 성장세를 기반으로 북미 공략을 한층 강화할 계획이다. 현지 유통망을 추가로 확대하고, 다양한 맛과 제품군을 통해 소비자 접점을 넓힌다는 전략이다.</t>
         </is>
       </c>
+      <c r="H111" t="n">
+        <v>417293221</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026.04.10 12:07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>참고하나해주면[2]</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>얘가 오늘 못가고있지?
+만약 주말사이에 글로벌악재뉴스떠서 월욜 하락장나오면말이다
+이놈은 오늘 못올랐기때매 월욜에 덜빠지거나 안빠질수있다~ ㅇㅋ?</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" t="n">
+        <v>183</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>참고하나해주면[2] 얘가 오늘 못가고있지?
+만약 주말사이에 글로벌악재뉴스떠서 월욜 하락장나오면말이다
+이놈은 오늘 못올랐기때매 월욜에 덜빠지거나 안빠질수있다~ ㅇㅋ?</t>
+        </is>
+      </c>
       <c r="H112" t="n">
-        <v>417293221</v>
+        <v>417293168</v>
       </c>
     </row>
     <row r="113">
@@ -7006,30 +7022,32 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>삼성증권으로 오세요. 5% 상승중</t>
+          <t>시총 37조짜리가</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>삼성증권 5%</t>
+          <t>잡주처럼 움직이노
+잡주맞네ㅋㅋㅋㅋㅋㅋ</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E172" t="n">
         <v>2</v>
       </c>
       <c r="F172" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>삼성증권으로 오세요. 5% 상승중 삼성증권 5%</t>
+          <t>시총 37조짜리가 잡주처럼 움직이노
+잡주맞네ㅋㅋㅋㅋㅋㅋ</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>417268556</v>
+        <v>417268564</v>
       </c>
     </row>
     <row r="173">
@@ -7040,32 +7058,30 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>시총 37조짜리가</t>
+          <t>삼성증권으로 오세요. 5% 상승중</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>잡주처럼 움직이노
-잡주맞네ㅋㅋㅋㅋㅋㅋ</t>
+          <t>삼성증권 5%</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
         <v>2</v>
       </c>
       <c r="F173" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>시총 37조짜리가 잡주처럼 움직이노
-잡주맞네ㅋㅋㅋㅋㅋㅋ</t>
+          <t>삼성증권으로 오세요. 5% 상승중 삼성증권 5%</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>417268564</v>
+        <v>417268556</v>
       </c>
     </row>
     <row r="174">
@@ -8104,30 +8120,30 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>얘만 뭐냐[1]</t>
+          <t>ㅋㅋㅋㅋㅋ 속았누 다들</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>증권주 전부날라가는데 혼자 파랭이네</t>
+          <t>다른걸러 물타야겟누</t>
         </is>
       </c>
       <c r="D203" t="n">
+        <v>4</v>
+      </c>
+      <c r="E203" t="n">
         <v>2</v>
       </c>
-      <c r="E203" t="n">
-        <v>1</v>
-      </c>
       <c r="F203" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>얘만 뭐냐[1] 증권주 전부날라가는데 혼자 파랭이네</t>
+          <t>ㅋㅋㅋㅋㅋ 속았누 다들 다른걸러 물타야겟누</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>417260541</v>
+        <v>417260542</v>
       </c>
     </row>
     <row r="204">
@@ -8138,30 +8154,30 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ㅋㅋㅋㅋㅋ 속았누 다들</t>
+          <t>얘만 뭐냐[1]</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>다른걸러 물타야겟누</t>
+          <t>증권주 전부날라가는데 혼자 파랭이네</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F204" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>ㅋㅋㅋㅋㅋ 속았누 다들 다른걸러 물타야겟누</t>
+          <t>얘만 뭐냐[1] 증권주 전부날라가는데 혼자 파랭이네</t>
         </is>
       </c>
       <c r="H204" t="n">
-        <v>417260542</v>
+        <v>417260541</v>
       </c>
     </row>
     <row r="205">
@@ -10336,80 +10352,10 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>미에증 계좌로 주식을 옮겨야 하겠네..</t>
+          <t>오메</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
-        <is>
-          <t>스X 공모주 관련 먼가 이벤트를 할거 같은데..</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>19</v>
-      </c>
-      <c r="E266" t="n">
-        <v>2</v>
-      </c>
-      <c r="F266" t="n">
-        <v>185</v>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>미에증 계좌로 주식을 옮겨야 하겠네.. 스X 공모주 관련 먼가 이벤트를 할거 같은데..</t>
-        </is>
-      </c>
-      <c r="H266" t="n">
-        <v>417217474</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>2026.04.09 15:35</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>이러면 오늘 종가는?[4]</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7만원 넘는다
-털린 개미들만  불쌍하다 </t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>40</v>
-      </c>
-      <c r="E267" t="n">
-        <v>4</v>
-      </c>
-      <c r="F267" t="n">
-        <v>563</v>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이러면 오늘 종가는?[4] 7만원 넘는다
-털린 개미들만  불쌍하다 </t>
-        </is>
-      </c>
-      <c r="H267" t="n">
-        <v>417217550</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2026.04.09 15:35</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>오메</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
         <is>
           <t>옵션만기일 잘 방어해줬네
 미래는 삼전 닉스등 코스피지수에 
@@ -10417,16 +10363,16 @@
 왠일로 휩쓸리지 않고 마감 잘했네</t>
         </is>
       </c>
-      <c r="D268" t="n">
+      <c r="D266" t="n">
         <v>29</v>
       </c>
-      <c r="E268" t="n">
+      <c r="E266" t="n">
         <v>1</v>
       </c>
-      <c r="F268" t="n">
+      <c r="F266" t="n">
         <v>132</v>
       </c>
-      <c r="G268" t="inlineStr">
+      <c r="G266" t="inlineStr">
         <is>
           <t>오메 옵션만기일 잘 방어해줬네
 미래는 삼전 닉스등 코스피지수에 
@@ -10434,8 +10380,78 @@
 왠일로 휩쓸리지 않고 마감 잘했네</t>
         </is>
       </c>
+      <c r="H266" t="n">
+        <v>417217509</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026.04.09 15:35</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>미에증 계좌로 주식을 옮겨야 하겠네..</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>스X 공모주 관련 먼가 이벤트를 할거 같은데..</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>19</v>
+      </c>
+      <c r="E267" t="n">
+        <v>2</v>
+      </c>
+      <c r="F267" t="n">
+        <v>185</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>미에증 계좌로 주식을 옮겨야 하겠네.. 스X 공모주 관련 먼가 이벤트를 할거 같은데..</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>417217474</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026.04.09 15:35</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>이러면 오늘 종가는?[4]</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7만원 넘는다
+털린 개미들만  불쌍하다 </t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>40</v>
+      </c>
+      <c r="E268" t="n">
+        <v>4</v>
+      </c>
+      <c r="F268" t="n">
+        <v>563</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이러면 오늘 종가는?[4] 7만원 넘는다
+털린 개미들만  불쌍하다 </t>
+        </is>
+      </c>
       <c r="H268" t="n">
-        <v>417217509</v>
+        <v>417217550</v>
       </c>
     </row>
     <row r="269">
@@ -11958,30 +11974,30 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>살려주세요[1]</t>
+          <t>이란전쟁 종전 협상 상황</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>열심히 잘 살겠습니다.</t>
+          <t>백악관은 밴스 부통령이 오는 11일 파키스탄 이슬라마바드에서 열릴 미국-이란 종전 협상에 대표단을 이끌고 참석할 예정이라고 밝혔다.</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E311" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F311" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>살려주세요[1] 열심히 잘 살겠습니다.</t>
+          <t>이란전쟁 종전 협상 상황 백악관은 밴스 부통령이 오는 11일 파키스탄 이슬라마바드에서 열릴 미국-이란 종전 협상에 대표단을 이끌고 참석할 예정이라고 밝혔다.</t>
         </is>
       </c>
       <c r="H311" t="n">
-        <v>417171705</v>
+        <v>417171754</v>
       </c>
     </row>
     <row r="312">
@@ -11992,30 +12008,30 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>이란전쟁 종전 협상 상황</t>
+          <t>살려주세요[1]</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>백악관은 밴스 부통령이 오는 11일 파키스탄 이슬라마바드에서 열릴 미국-이란 종전 협상에 대표단을 이끌고 참석할 예정이라고 밝혔다.</t>
+          <t>열심히 잘 살겠습니다.</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E312" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F312" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>이란전쟁 종전 협상 상황 백악관은 밴스 부통령이 오는 11일 파키스탄 이슬라마바드에서 열릴 미국-이란 종전 협상에 대표단을 이끌고 참석할 예정이라고 밝혔다.</t>
+          <t>살려주세요[1] 열심히 잘 살겠습니다.</t>
         </is>
       </c>
       <c r="H312" t="n">
-        <v>417171754</v>
+        <v>417171705</v>
       </c>
     </row>
     <row r="313">
@@ -15324,68 +15340,68 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
+          <t>단단</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>묵직
+하구만</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>15</v>
+      </c>
+      <c r="E405" t="n">
+        <v>1</v>
+      </c>
+      <c r="F405" t="n">
+        <v>117</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>단단 묵직
+하구만</t>
+        </is>
+      </c>
+      <c r="H405" t="n">
+        <v>417129670</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026.04.08 19:51</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
           <t>지금 매도 노</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr">
+      <c r="C406" t="inlineStr">
         <is>
           <t>내일들 봅시다
 이왕 참고 인내 하신거</t>
         </is>
       </c>
-      <c r="D405" t="n">
+      <c r="D406" t="n">
         <v>14</v>
       </c>
-      <c r="E405" t="n">
+      <c r="E406" t="n">
         <v>1</v>
       </c>
-      <c r="F405" t="n">
+      <c r="F406" t="n">
         <v>117</v>
       </c>
-      <c r="G405" t="inlineStr">
+      <c r="G406" t="inlineStr">
         <is>
           <t>지금 매도 노 내일들 봅시다
 이왕 참고 인내 하신거</t>
         </is>
       </c>
-      <c r="H405" t="n">
+      <c r="H406" t="n">
         <v>417129669</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>2026.04.08 19:51</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>단단</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>묵직
-하구만</t>
-        </is>
-      </c>
-      <c r="D406" t="n">
-        <v>15</v>
-      </c>
-      <c r="E406" t="n">
-        <v>1</v>
-      </c>
-      <c r="F406" t="n">
-        <v>117</v>
-      </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>단단 묵직
-하구만</t>
-        </is>
-      </c>
-      <c r="H406" t="n">
-        <v>417129670</v>
       </c>
     </row>
     <row r="407">
@@ -17036,30 +17052,30 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>코스피 6000이 코앞이다</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>ㅋㅋㅋㅋ겹겹이 호재만발</t>
+          <t>주차하겠네</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E451" t="n">
         <v>0</v>
       </c>
       <c r="F451" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>코스피 6000이 코앞이다 ㅋㅋㅋㅋ겹겹이 호재만발</t>
+          <t>68 주차하겠네</t>
         </is>
       </c>
       <c r="H451" t="n">
-        <v>417109542</v>
+        <v>417109623</v>
       </c>
     </row>
     <row r="452">
@@ -17070,30 +17086,30 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>코스피 6000이 코앞이다</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>주차하겠네</t>
+          <t>ㅋㅋㅋㅋ겹겹이 호재만발</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E452" t="n">
         <v>0</v>
       </c>
       <c r="F452" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>68 주차하겠네</t>
+          <t>코스피 6000이 코앞이다 ㅋㅋㅋㅋ겹겹이 호재만발</t>
         </is>
       </c>
       <c r="H452" t="n">
-        <v>417109623</v>
+        <v>417109542</v>
       </c>
     </row>
     <row r="453">
@@ -21392,30 +21408,30 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>꽉 쥐어라 오늘이 숏 커버링이네</t>
+          <t>참 돈벌기 쉽다.. 인간띠 두르면 폭격 못한다 ...</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>고고고고고</t>
+          <t xml:space="preserve">원숭이도 알겠다..  </t>
         </is>
       </c>
       <c r="D574" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E574" t="n">
         <v>0</v>
       </c>
       <c r="F574" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>꽉 쥐어라 오늘이 숏 커버링이네 고고고고고</t>
+          <t xml:space="preserve">참 돈벌기 쉽다.. 인간띠 두르면 폭격 못한다 ... 원숭이도 알겠다..  </t>
         </is>
       </c>
       <c r="H574" t="n">
-        <v>417027842</v>
+        <v>417027796</v>
       </c>
     </row>
     <row r="575">
@@ -21426,30 +21442,30 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>참 돈벌기 쉽다.. 인간띠 두르면 폭격 못한다 ...</t>
+          <t>오늘 본장에 숏커버링 수급!!</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t xml:space="preserve">원숭이도 알겠다..  </t>
+          <t>오후 장에서 본격적 시작으로 보리</t>
         </is>
       </c>
       <c r="D575" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E575" t="n">
         <v>0</v>
       </c>
       <c r="F575" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t xml:space="preserve">참 돈벌기 쉽다.. 인간띠 두르면 폭격 못한다 ... 원숭이도 알겠다..  </t>
+          <t>오늘 본장에 숏커버링 수급!! 오후 장에서 본격적 시작으로 보리</t>
         </is>
       </c>
       <c r="H575" t="n">
-        <v>417027796</v>
+        <v>417027809</v>
       </c>
     </row>
     <row r="576">
@@ -21460,12 +21476,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>니 오늘 상 좀 쳐라[1]</t>
+          <t>꽉 쥐어라 오늘이 숏 커버링이네</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>그럴때 됐잖아!</t>
+          <t>고고고고고</t>
         </is>
       </c>
       <c r="D576" t="n">
@@ -21475,15 +21491,15 @@
         <v>0</v>
       </c>
       <c r="F576" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>니 오늘 상 좀 쳐라[1] 그럴때 됐잖아!</t>
+          <t>꽉 쥐어라 오늘이 숏 커버링이네 고고고고고</t>
         </is>
       </c>
       <c r="H576" t="n">
-        <v>417027874</v>
+        <v>417027842</v>
       </c>
     </row>
     <row r="577">
@@ -21494,30 +21510,30 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>오늘 본장에 숏커버링 수급!!</t>
+          <t>니 오늘 상 좀 쳐라[1]</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>오후 장에서 본격적 시작으로 보리</t>
+          <t>그럴때 됐잖아!</t>
         </is>
       </c>
       <c r="D577" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E577" t="n">
         <v>0</v>
       </c>
       <c r="F577" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>오늘 본장에 숏커버링 수급!! 오후 장에서 본격적 시작으로 보리</t>
+          <t>니 오늘 상 좀 쳐라[1] 그럴때 됐잖아!</t>
         </is>
       </c>
       <c r="H577" t="n">
-        <v>417027809</v>
+        <v>417027874</v>
       </c>
     </row>
     <row r="578">
@@ -21986,30 +22002,30 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>헐... 22프로 상승중[2]</t>
+          <t>와~~우</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>뭔데 이렇게 쩜상하냐</t>
+          <t>또람프2주간휴전동의~~~~~ ㅎㅎ</t>
         </is>
       </c>
       <c r="D591" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E591" t="n">
         <v>0</v>
       </c>
       <c r="F591" t="n">
-        <v>170</v>
+        <v>36</v>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>헐... 22프로 상승중[2] 뭔데 이렇게 쩜상하냐</t>
+          <t>와~~우 또람프2주간휴전동의~~~~~ ㅎㅎ</t>
         </is>
       </c>
       <c r="H591" t="n">
-        <v>417024142</v>
+        <v>417024213</v>
       </c>
     </row>
     <row r="592">
@@ -22020,30 +22036,30 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>와~~우</t>
+          <t>헐... 22프로 상승중[2]</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>또람프2주간휴전동의~~~~~ ㅎㅎ</t>
+          <t>뭔데 이렇게 쩜상하냐</t>
         </is>
       </c>
       <c r="D592" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E592" t="n">
         <v>0</v>
       </c>
       <c r="F592" t="n">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>와~~우 또람프2주간휴전동의~~~~~ ㅎㅎ</t>
+          <t>헐... 22프로 상승중[2] 뭔데 이렇게 쩜상하냐</t>
         </is>
       </c>
       <c r="H592" t="n">
-        <v>417024213</v>
+        <v>417024142</v>
       </c>
     </row>
     <row r="593">
@@ -28108,30 +28124,32 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>ㅋㅋㅋㅋ 어제 오후에도 이랬다 ㅋㅋㅋ[1]</t>
+          <t>합의가 아니라 수령이야[2]</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>실적좋다고 오늘 무조건 오른다고했는데 박았지? 내일도 그냥 비슷할듯 희망 가지지마 더아플 뿐이다</t>
+          <t>슬슬 물고 빠는 애들 나오기 시작하네
+이잡주가 가것냐?</t>
         </is>
       </c>
       <c r="D762" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E762" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F762" t="n">
-        <v>136</v>
+        <v>359</v>
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>ㅋㅋㅋㅋ 어제 오후에도 이랬다 ㅋㅋㅋ[1] 실적좋다고 오늘 무조건 오른다고했는데 박았지? 내일도 그냥 비슷할듯 희망 가지지마 더아플 뿐이다</t>
+          <t>합의가 아니라 수령이야[2] 슬슬 물고 빠는 애들 나오기 시작하네
+이잡주가 가것냐?</t>
         </is>
       </c>
       <c r="H762" t="n">
-        <v>416868169</v>
+        <v>416868277</v>
       </c>
     </row>
     <row r="763">
@@ -28142,32 +28160,30 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>합의가 아니라 수령이야[2]</t>
+          <t>ㅋㅋㅋㅋ 어제 오후에도 이랬다 ㅋㅋㅋ[1]</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>슬슬 물고 빠는 애들 나오기 시작하네
-이잡주가 가것냐?</t>
+          <t>실적좋다고 오늘 무조건 오른다고했는데 박았지? 내일도 그냥 비슷할듯 희망 가지지마 더아플 뿐이다</t>
         </is>
       </c>
       <c r="D763" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E763" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F763" t="n">
-        <v>359</v>
+        <v>136</v>
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>합의가 아니라 수령이야[2] 슬슬 물고 빠는 애들 나오기 시작하네
-이잡주가 가것냐?</t>
+          <t>ㅋㅋㅋㅋ 어제 오후에도 이랬다 ㅋㅋㅋ[1] 실적좋다고 오늘 무조건 오른다고했는데 박았지? 내일도 그냥 비슷할듯 희망 가지지마 더아플 뿐이다</t>
         </is>
       </c>
       <c r="H763" t="n">
-        <v>416868277</v>
+        <v>416868169</v>
       </c>
     </row>
     <row r="764">
@@ -30804,10 +30820,50 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
+          <t>미래에셋증권 보셔야겠네요</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>확인은 하고 가셔야겠네요
+들고 계신 분들은 한 번 확인해보셔야겠습니다
+미래에셋증권 관련 정리된 이야기들이 곧 공유될 듯합니다
+아직 모르시는 분들이 더 많은 분위기입니다</t>
+        </is>
+      </c>
+      <c r="D838" t="n">
+        <v>3</v>
+      </c>
+      <c r="E838" t="n">
+        <v>1</v>
+      </c>
+      <c r="F838" t="n">
+        <v>66</v>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>미래에셋증권 보셔야겠네요 확인은 하고 가셔야겠네요
+들고 계신 분들은 한 번 확인해보셔야겠습니다
+미래에셋증권 관련 정리된 이야기들이 곧 공유될 듯합니다
+아직 모르시는 분들이 더 많은 분위기입니다</t>
+        </is>
+      </c>
+      <c r="H838" t="n">
+        <v>416817160</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026.04.06 09:52</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
           <t>주식 상식!! 재료는 6개월 선반영 기초중의 ...</t>
         </is>
       </c>
-      <c r="C838" t="inlineStr">
+      <c r="C839" t="inlineStr">
         <is>
           <t>진짜 주식에 대해서 일자무식인 사람들 많네 ㅎㅎ
 이런 호재에 왜 빌빌 거리냐고? ㅎㅎ
@@ -30818,16 +30874,16 @@
 지금 63일때라도 빨리 팔아라 ㅋㅋㅋ</t>
         </is>
       </c>
-      <c r="D838" t="n">
+      <c r="D839" t="n">
         <v>4</v>
       </c>
-      <c r="E838" t="n">
+      <c r="E839" t="n">
         <v>2</v>
       </c>
-      <c r="F838" t="n">
+      <c r="F839" t="n">
         <v>58</v>
       </c>
-      <c r="G838" t="inlineStr">
+      <c r="G839" t="inlineStr">
         <is>
           <t>주식 상식!! 재료는 6개월 선반영 기초중의 ... 진짜 주식에 대해서 일자무식인 사람들 많네 ㅎㅎ
 이런 호재에 왜 빌빌 거리냐고? ㅎㅎ
@@ -30838,48 +30894,8 @@
 지금 63일때라도 빨리 팔아라 ㅋㅋㅋ</t>
         </is>
       </c>
-      <c r="H838" t="n">
+      <c r="H839" t="n">
         <v>416817102</v>
-      </c>
-    </row>
-    <row r="839">
-      <c r="A839" t="inlineStr">
-        <is>
-          <t>2026.04.06 09:52</t>
-        </is>
-      </c>
-      <c r="B839" t="inlineStr">
-        <is>
-          <t>미래에셋증권 보셔야겠네요</t>
-        </is>
-      </c>
-      <c r="C839" t="inlineStr">
-        <is>
-          <t>확인은 하고 가셔야겠네요
-들고 계신 분들은 한 번 확인해보셔야겠습니다
-미래에셋증권 관련 정리된 이야기들이 곧 공유될 듯합니다
-아직 모르시는 분들이 더 많은 분위기입니다</t>
-        </is>
-      </c>
-      <c r="D839" t="n">
-        <v>3</v>
-      </c>
-      <c r="E839" t="n">
-        <v>1</v>
-      </c>
-      <c r="F839" t="n">
-        <v>66</v>
-      </c>
-      <c r="G839" t="inlineStr">
-        <is>
-          <t>미래에셋증권 보셔야겠네요 확인은 하고 가셔야겠네요
-들고 계신 분들은 한 번 확인해보셔야겠습니다
-미래에셋증권 관련 정리된 이야기들이 곧 공유될 듯합니다
-아직 모르시는 분들이 더 많은 분위기입니다</t>
-        </is>
-      </c>
-      <c r="H839" t="n">
-        <v>416817160</v>
       </c>
     </row>
     <row r="840">
@@ -31348,40 +31364,10 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>새로운 리서치가 있어요 📝</t>
-        </is>
-      </c>
-      <c r="C853" t="inlineStr"/>
-      <c r="D853" t="n">
-        <v>5</v>
-      </c>
-      <c r="E853" t="n">
-        <v>0</v>
-      </c>
-      <c r="F853" t="n">
-        <v>179</v>
-      </c>
-      <c r="G853" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새로운 리서치가 있어요 📝 </t>
-        </is>
-      </c>
-      <c r="H853" t="n">
-        <v>416811622</v>
-      </c>
-    </row>
-    <row r="854">
-      <c r="A854" t="inlineStr">
-        <is>
-          <t>2026.04.06 09:25</t>
-        </is>
-      </c>
-      <c r="B854" t="inlineStr">
-        <is>
           <t>이놈도 이제 끝물</t>
         </is>
       </c>
-      <c r="C854" t="inlineStr">
+      <c r="C853" t="inlineStr">
         <is>
           <t>스페이스x  이제 그만좀  울거먹어라
 미래에셋증권은
@@ -31389,16 +31375,16 @@
 설거지타임</t>
         </is>
       </c>
-      <c r="D854" t="n">
+      <c r="D853" t="n">
         <v>4</v>
       </c>
-      <c r="E854" t="n">
+      <c r="E853" t="n">
         <v>2</v>
       </c>
-      <c r="F854" t="n">
+      <c r="F853" t="n">
         <v>39</v>
       </c>
-      <c r="G854" t="inlineStr">
+      <c r="G853" t="inlineStr">
         <is>
           <t>이놈도 이제 끝물 스페이스x  이제 그만좀  울거먹어라
 미래에셋증권은
@@ -31406,8 +31392,38 @@
 설거지타임</t>
         </is>
       </c>
+      <c r="H853" t="n">
+        <v>416811735</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026.04.06 09:25</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>새로운 리서치가 있어요 📝</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr"/>
+      <c r="D854" t="n">
+        <v>5</v>
+      </c>
+      <c r="E854" t="n">
+        <v>0</v>
+      </c>
+      <c r="F854" t="n">
+        <v>179</v>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새로운 리서치가 있어요 📝 </t>
+        </is>
+      </c>
       <c r="H854" t="n">
-        <v>416811735</v>
+        <v>416811622</v>
       </c>
     </row>
     <row r="855">
@@ -32492,30 +32508,30 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>전고점 뚫으면 좋겠습니다 ㅠㅠ</t>
+          <t>아침부터 장난질인거 보니 오늘 떡상하겠다</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>제 소원입니다 ㅜㅜㅋ</t>
+          <t>다들 성투합시다</t>
         </is>
       </c>
       <c r="D886" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E886" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F886" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>전고점 뚫으면 좋겠습니다 ㅠㅠ 제 소원입니다 ㅜㅜㅋ</t>
+          <t>아침부터 장난질인거 보니 오늘 떡상하겠다 다들 성투합시다</t>
         </is>
       </c>
       <c r="H886" t="n">
-        <v>416801185</v>
+        <v>416801228</v>
       </c>
     </row>
     <row r="887">
@@ -32526,30 +32542,30 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>아침부터 장난질인거 보니 오늘 떡상하겠다</t>
+          <t>전고점 뚫으면 좋겠습니다 ㅠㅠ</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>다들 성투합시다</t>
+          <t>제 소원입니다 ㅜㅜㅋ</t>
         </is>
       </c>
       <c r="D887" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E887" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F887" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>아침부터 장난질인거 보니 오늘 떡상하겠다 다들 성투합시다</t>
+          <t>전고점 뚫으면 좋겠습니다 ㅠㅠ 제 소원입니다 ㅜㅜㅋ</t>
         </is>
       </c>
       <c r="H887" t="n">
-        <v>416801228</v>
+        <v>416801185</v>
       </c>
     </row>
     <row r="888">
@@ -40608,30 +40624,32 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>또람프[1]</t>
+          <t>종가 맞추러 간다[1]</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>미장선물박살나고있는데 이인간자고일어나면 또 말바꾼다~~~ 완화메세지낸다~~~  결국손해보는건 아시아증시그중(한국 일본) 만 손실이크다~~~~  짜증나고  화난다~~~</t>
+          <t>ㅎㅎ 오늘도 수고 하셨습니다
+내일은 또 무슨 뉴스가 나올지 ㅎㅎ</t>
         </is>
       </c>
       <c r="D1102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E1102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1102" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G1102" t="inlineStr">
         <is>
-          <t>또람프[1] 미장선물박살나고있는데 이인간자고일어나면 또 말바꾼다~~~ 완화메세지낸다~~~  결국손해보는건 아시아증시그중(한국 일본) 만 손실이크다~~~~  짜증나고  화난다~~~</t>
+          <t>종가 맞추러 간다[1] ㅎㅎ 오늘도 수고 하셨습니다
+내일은 또 무슨 뉴스가 나올지 ㅎㅎ</t>
         </is>
       </c>
       <c r="H1102" t="n">
-        <v>416631383</v>
+        <v>416631385</v>
       </c>
     </row>
     <row r="1103">
@@ -40642,32 +40660,30 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>종가 맞추러 간다[1]</t>
+          <t>또람프[1]</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>ㅎㅎ 오늘도 수고 하셨습니다
-내일은 또 무슨 뉴스가 나올지 ㅎㅎ</t>
+          <t>미장선물박살나고있는데 이인간자고일어나면 또 말바꾼다~~~ 완화메세지낸다~~~  결국손해보는건 아시아증시그중(한국 일본) 만 손실이크다~~~~  짜증나고  화난다~~~</t>
         </is>
       </c>
       <c r="D1103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E1103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1103" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G1103" t="inlineStr">
         <is>
-          <t>종가 맞추러 간다[1] ㅎㅎ 오늘도 수고 하셨습니다
-내일은 또 무슨 뉴스가 나올지 ㅎㅎ</t>
+          <t>또람프[1] 미장선물박살나고있는데 이인간자고일어나면 또 말바꾼다~~~ 완화메세지낸다~~~  결국손해보는건 아시아증시그중(한국 일본) 만 손실이크다~~~~  짜증나고  화난다~~~</t>
         </is>
       </c>
       <c r="H1103" t="n">
-        <v>416631385</v>
+        <v>416631383</v>
       </c>
     </row>
     <row r="1104">
@@ -42874,102 +42890,102 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>어제 점심에 못판 흑우 없제?[1]</t>
+          <t>환율 2000원 가겄다..2-3주간 계속 오를...</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
-        <is>
-          <t>흐름이 지난주랑 똑같은데 이번엔 다를꺼야 한친구들은 예적금이나 해라</t>
-        </is>
-      </c>
-      <c r="D1164" t="n">
-        <v>2</v>
-      </c>
-      <c r="E1164" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1164" t="n">
-        <v>48</v>
-      </c>
-      <c r="G1164" t="inlineStr">
-        <is>
-          <t>어제 점심에 못판 흑우 없제?[1] 흐름이 지난주랑 똑같은데 이번엔 다를꺼야 한친구들은 예적금이나 해라</t>
-        </is>
-      </c>
-      <c r="H1164" t="n">
-        <v>416587235</v>
-      </c>
-    </row>
-    <row r="1165">
-      <c r="A1165" t="inlineStr">
-        <is>
-          <t>2026.04.02 11:15</t>
-        </is>
-      </c>
-      <c r="B1165" t="inlineStr">
-        <is>
-          <t>트럼프</t>
-        </is>
-      </c>
-      <c r="C1165" t="inlineStr">
-        <is>
-          <t>너임마청년이냐?</t>
-        </is>
-      </c>
-      <c r="D1165" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1165" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1165" t="n">
-        <v>5</v>
-      </c>
-      <c r="G1165" t="inlineStr">
-        <is>
-          <t>트럼프 너임마청년이냐?</t>
-        </is>
-      </c>
-      <c r="H1165" t="n">
-        <v>416587260</v>
-      </c>
-    </row>
-    <row r="1166">
-      <c r="A1166" t="inlineStr">
-        <is>
-          <t>2026.04.02 11:15</t>
-        </is>
-      </c>
-      <c r="B1166" t="inlineStr">
-        <is>
-          <t>환율 2000원 가겄다..2-3주간 계속 오를...</t>
-        </is>
-      </c>
-      <c r="C1166" t="inlineStr">
         <is>
           <t>뭐여..
 2,3주간 환율, 유가 오를거고,,,
 주식은 어떻게 될까 ? 생각은 자유,,</t>
         </is>
       </c>
-      <c r="D1166" t="n">
+      <c r="D1164" t="n">
         <v>3</v>
       </c>
-      <c r="E1166" t="n">
+      <c r="E1164" t="n">
         <v>1</v>
       </c>
-      <c r="F1166" t="n">
+      <c r="F1164" t="n">
         <v>54</v>
       </c>
-      <c r="G1166" t="inlineStr">
+      <c r="G1164" t="inlineStr">
         <is>
           <t>환율 2000원 가겄다..2-3주간 계속 오를... 뭐여..
 2,3주간 환율, 유가 오를거고,,,
 주식은 어떻게 될까 ? 생각은 자유,,</t>
         </is>
       </c>
+      <c r="H1164" t="n">
+        <v>416587264</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026.04.02 11:15</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>트럼프</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>너임마청년이냐?</t>
+        </is>
+      </c>
+      <c r="D1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>트럼프 너임마청년이냐?</t>
+        </is>
+      </c>
+      <c r="H1165" t="n">
+        <v>416587260</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026.04.02 11:15</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>어제 점심에 못판 흑우 없제?[1]</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>흐름이 지난주랑 똑같은데 이번엔 다를꺼야 한친구들은 예적금이나 해라</t>
+        </is>
+      </c>
+      <c r="D1166" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>어제 점심에 못판 흑우 없제?[1] 흐름이 지난주랑 똑같은데 이번엔 다를꺼야 한친구들은 예적금이나 해라</t>
+        </is>
+      </c>
       <c r="H1166" t="n">
-        <v>416587264</v>
+        <v>416587235</v>
       </c>
     </row>
     <row r="1167">
@@ -43994,30 +44010,34 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>시장이 놀랏네 이건 스페이스 x 주식임</t>
+          <t>대박ㅡhd현대솔루션</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t xml:space="preserve">도람프 때문에 전세계가 난리군 </t>
+          <t>도람프왈 : 전세계는 알아서 자립하라 ㅡㅡ
+에너지도 자립, 국방도 자립
+두개 관련 주가 떡상</t>
         </is>
       </c>
       <c r="D1195" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E1195" t="n">
         <v>0</v>
       </c>
       <c r="F1195" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G1195" t="inlineStr">
         <is>
-          <t xml:space="preserve">시장이 놀랏네 이건 스페이스 x 주식임 도람프 때문에 전세계가 난리군 </t>
+          <t>대박ㅡhd현대솔루션 도람프왈 : 전세계는 알아서 자립하라 ㅡㅡ
+에너지도 자립, 국방도 자립
+두개 관련 주가 떡상</t>
         </is>
       </c>
       <c r="H1195" t="n">
-        <v>416576645</v>
+        <v>416576761</v>
       </c>
     </row>
     <row r="1196">
@@ -44028,72 +44048,72 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
+          <t>미국과 중국 러시아 우주산업</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>미국이 달에 우주선보내고 이제 행성 땅 따먹기
+새로운 시작이다
+한국도 발 담그자</t>
+        </is>
+      </c>
+      <c r="D1196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>51</v>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>미국과 중국 러시아 우주산업 미국이 달에 우주선보내고 이제 행성 땅 따먹기
+새로운 시작이다
+한국도 발 담그자</t>
+        </is>
+      </c>
+      <c r="H1196" t="n">
+        <v>416576776</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026.04.02 10:34</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
           <t>하</t>
         </is>
       </c>
-      <c r="C1196" t="inlineStr">
+      <c r="C1197" t="inlineStr">
         <is>
           <t>아니 뭣같은게 코스피 2프로 빠지는데 얘는 6프로 빠지고
 코스피 8프로 오르면 얘는 3프로 오르고
 뭐 이런 개잡주가 다있노</t>
         </is>
       </c>
-      <c r="D1196" t="n">
+      <c r="D1197" t="n">
         <v>5</v>
       </c>
-      <c r="E1196" t="n">
+      <c r="E1197" t="n">
         <v>0</v>
       </c>
-      <c r="F1196" t="n">
+      <c r="F1197" t="n">
         <v>24</v>
       </c>
-      <c r="G1196" t="inlineStr">
+      <c r="G1197" t="inlineStr">
         <is>
           <t>하 아니 뭣같은게 코스피 2프로 빠지는데 얘는 6프로 빠지고
 코스피 8프로 오르면 얘는 3프로 오르고
 뭐 이런 개잡주가 다있노</t>
         </is>
       </c>
-      <c r="H1196" t="n">
+      <c r="H1197" t="n">
         <v>416576580</v>
-      </c>
-    </row>
-    <row r="1197">
-      <c r="A1197" t="inlineStr">
-        <is>
-          <t>2026.04.02 10:34</t>
-        </is>
-      </c>
-      <c r="B1197" t="inlineStr">
-        <is>
-          <t>대박ㅡhd현대솔루션</t>
-        </is>
-      </c>
-      <c r="C1197" t="inlineStr">
-        <is>
-          <t>도람프왈 : 전세계는 알아서 자립하라 ㅡㅡ
-에너지도 자립, 국방도 자립
-두개 관련 주가 떡상</t>
-        </is>
-      </c>
-      <c r="D1197" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1197" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1197" t="n">
-        <v>56</v>
-      </c>
-      <c r="G1197" t="inlineStr">
-        <is>
-          <t>대박ㅡhd현대솔루션 도람프왈 : 전세계는 알아서 자립하라 ㅡㅡ
-에너지도 자립, 국방도 자립
-두개 관련 주가 떡상</t>
-        </is>
-      </c>
-      <c r="H1197" t="n">
-        <v>416576761</v>
       </c>
     </row>
     <row r="1198">
@@ -44104,34 +44124,30 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>미국과 중국 러시아 우주산업</t>
+          <t>시장이 놀랏네 이건 스페이스 x 주식임</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>미국이 달에 우주선보내고 이제 행성 땅 따먹기
-새로운 시작이다
-한국도 발 담그자</t>
+          <t xml:space="preserve">도람프 때문에 전세계가 난리군 </t>
         </is>
       </c>
       <c r="D1198" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E1198" t="n">
         <v>0</v>
       </c>
       <c r="F1198" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G1198" t="inlineStr">
         <is>
-          <t>미국과 중국 러시아 우주산업 미국이 달에 우주선보내고 이제 행성 땅 따먹기
-새로운 시작이다
-한국도 발 담그자</t>
+          <t xml:space="preserve">시장이 놀랏네 이건 스페이스 x 주식임 도람프 때문에 전세계가 난리군 </t>
         </is>
       </c>
       <c r="H1198" t="n">
-        <v>416576776</v>
+        <v>416576645</v>
       </c>
     </row>
     <row r="1199">
@@ -44498,30 +44514,30 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>참 공매도를 이길수가</t>
+          <t>오늘 도람프 왜나온지 아시는분?</t>
         </is>
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>없군아,,, 재들은 손실볼일 없어 좋것네,,,무조건 수익이네~~</t>
+          <t>관종이다 그냥..</t>
         </is>
       </c>
       <c r="D1209" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1209" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G1209" t="inlineStr">
         <is>
-          <t>참 공매도를 이길수가 없군아,,, 재들은 손실볼일 없어 좋것네,,,무조건 수익이네~~</t>
+          <t>오늘 도람프 왜나온지 아시는분? 관종이다 그냥..</t>
         </is>
       </c>
       <c r="H1209" t="n">
-        <v>416573151</v>
+        <v>416572953</v>
       </c>
     </row>
     <row r="1210">
@@ -44532,30 +44548,32 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>오늘 도람프 왜나온지 아시는분?</t>
+          <t>트럼프 요약) 앞으로 2주~3주 더 강력한 공...</t>
         </is>
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>관종이다 그냥..</t>
+          <t>이란 석기시대로 돌려놓을것
+호르무즈 관련국가들이 알아서 해결해라</t>
         </is>
       </c>
       <c r="D1210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E1210" t="n">
         <v>0</v>
       </c>
       <c r="F1210" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G1210" t="inlineStr">
         <is>
-          <t>오늘 도람프 왜나온지 아시는분? 관종이다 그냥..</t>
+          <t>트럼프 요약) 앞으로 2주~3주 더 강력한 공... 이란 석기시대로 돌려놓을것
+호르무즈 관련국가들이 알아서 해결해라</t>
         </is>
       </c>
       <c r="H1210" t="n">
-        <v>416572953</v>
+        <v>416573188</v>
       </c>
     </row>
     <row r="1211">
@@ -44566,32 +44584,30 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>트럼프 요약) 앞으로 2주~3주 더 강력한 공...</t>
+          <t>참 공매도를 이길수가</t>
         </is>
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>이란 석기시대로 돌려놓을것
-호르무즈 관련국가들이 알아서 해결해라</t>
+          <t>없군아,,, 재들은 손실볼일 없어 좋것네,,,무조건 수익이네~~</t>
         </is>
       </c>
       <c r="D1211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1211" t="n">
         <v>2</v>
       </c>
-      <c r="E1211" t="n">
-        <v>0</v>
-      </c>
       <c r="F1211" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="G1211" t="inlineStr">
         <is>
-          <t>트럼프 요약) 앞으로 2주~3주 더 강력한 공... 이란 석기시대로 돌려놓을것
-호르무즈 관련국가들이 알아서 해결해라</t>
+          <t>참 공매도를 이길수가 없군아,,, 재들은 손실볼일 없어 좋것네,,,무조건 수익이네~~</t>
         </is>
       </c>
       <c r="H1211" t="n">
-        <v>416573188</v>
+        <v>416573151</v>
       </c>
     </row>
     <row r="1212">
@@ -47384,30 +47400,30 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>스페이스X, IPO 비공개 신청서 제출…6월 ...[1]</t>
+          <t>아르테미스2호 발사성공......오늘 상한가....[1]</t>
         </is>
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>오마이가트</t>
+          <t>오늘 종가는 무조건 상한가다,,,,,,,,ㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎ개미들 떨구고 5연상 가즈아......ㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎ</t>
         </is>
       </c>
       <c r="D1288" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E1288" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1288" t="n">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="G1288" t="inlineStr">
         <is>
-          <t>스페이스X, IPO 비공개 신청서 제출…6월 ...[1] 오마이가트</t>
+          <t>아르테미스2호 발사성공......오늘 상한가....[1] 오늘 종가는 무조건 상한가다,,,,,,,,ㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎ개미들 떨구고 5연상 가즈아......ㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎ</t>
         </is>
       </c>
       <c r="H1288" t="n">
-        <v>416548411</v>
+        <v>416548423</v>
       </c>
     </row>
     <row r="1289">
@@ -47418,30 +47434,30 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>아르테미스2호 발사성공......오늘 상한가....[1]</t>
+          <t>스페이스X, IPO 비공개 신청서 제출…6월 ...[1]</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>오늘 종가는 무조건 상한가다,,,,,,,,ㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎ개미들 떨구고 5연상 가즈아......ㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎ</t>
+          <t>오마이가트</t>
         </is>
       </c>
       <c r="D1289" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E1289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1289" t="n">
-        <v>246</v>
+        <v>95</v>
       </c>
       <c r="G1289" t="inlineStr">
         <is>
-          <t>아르테미스2호 발사성공......오늘 상한가....[1] 오늘 종가는 무조건 상한가다,,,,,,,,ㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎ개미들 떨구고 5연상 가즈아......ㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎㅎ</t>
+          <t>스페이스X, IPO 비공개 신청서 제출…6월 ...[1] 오마이가트</t>
         </is>
       </c>
       <c r="H1289" t="n">
-        <v>416548423</v>
+        <v>416548411</v>
       </c>
     </row>
     <row r="1290">
@@ -53646,30 +53662,30 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>오늘도 상한가 매도 걸고 시작 합시다</t>
+          <t>게임끝</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>공매도 장난 못치게요</t>
+          <t>상한가 ㅅㅅ</t>
         </is>
       </c>
       <c r="D1458" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1458" t="n">
         <v>0</v>
       </c>
       <c r="F1458" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G1458" t="inlineStr">
         <is>
-          <t>오늘도 상한가 매도 걸고 시작 합시다 공매도 장난 못치게요</t>
+          <t>게임끝 상한가 ㅅㅅ</t>
         </is>
       </c>
       <c r="H1458" t="n">
-        <v>416433017</v>
+        <v>416433119</v>
       </c>
     </row>
     <row r="1459">
@@ -53680,30 +53696,30 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>게임끝</t>
+          <t>오늘도 상한가 매도 걸고 시작 합시다</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>상한가 ㅅㅅ</t>
+          <t>공매도 장난 못치게요</t>
         </is>
       </c>
       <c r="D1459" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1459" t="n">
         <v>0</v>
       </c>
       <c r="F1459" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G1459" t="inlineStr">
         <is>
-          <t>게임끝 상한가 ㅅㅅ</t>
+          <t>오늘도 상한가 매도 걸고 시작 합시다 공매도 장난 못치게요</t>
         </is>
       </c>
       <c r="H1459" t="n">
-        <v>416433119</v>
+        <v>416433017</v>
       </c>
     </row>
     <row r="1460">
@@ -55336,30 +55352,32 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>외늠들 이제 9.6% 오늘 23만주매도...</t>
+          <t>전일자 대차잔고 수량대비  오늘 엄청 ...[2]</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>크 이제 팔게 없나? 오늘은 조금파네. 다행이다. 이제 개인과 기관이 사면 오른다. 다만 외인이 마지막 발악 조심해야함.</t>
+          <t>진짜 대단합니다 오늘 같은날  1프로대 마이너스면 개미들 승리입니다
+상한가 홀딩 쭈욱 이어갑시다</t>
         </is>
       </c>
       <c r="D1505" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E1505" t="n">
         <v>3</v>
       </c>
       <c r="F1505" t="n">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="G1505" t="inlineStr">
         <is>
-          <t>외늠들 이제 9.6% 오늘 23만주매도... 크 이제 팔게 없나? 오늘은 조금파네. 다행이다. 이제 개인과 기관이 사면 오른다. 다만 외인이 마지막 발악 조심해야함.</t>
+          <t>전일자 대차잔고 수량대비  오늘 엄청 ...[2] 진짜 대단합니다 오늘 같은날  1프로대 마이너스면 개미들 승리입니다
+상한가 홀딩 쭈욱 이어갑시다</t>
         </is>
       </c>
       <c r="H1505" t="n">
-        <v>416374913</v>
+        <v>416374950</v>
       </c>
     </row>
     <row r="1506">
@@ -55370,32 +55388,30 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>전일자 대차잔고 수량대비  오늘 엄청 ...[2]</t>
+          <t>외늠들 이제 9.6% 오늘 23만주매도...</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>진짜 대단합니다 오늘 같은날  1프로대 마이너스면 개미들 승리입니다
-상한가 홀딩 쭈욱 이어갑시다</t>
+          <t>크 이제 팔게 없나? 오늘은 조금파네. 다행이다. 이제 개인과 기관이 사면 오른다. 다만 외인이 마지막 발악 조심해야함.</t>
         </is>
       </c>
       <c r="D1506" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E1506" t="n">
         <v>3</v>
       </c>
       <c r="F1506" t="n">
-        <v>270</v>
+        <v>134</v>
       </c>
       <c r="G1506" t="inlineStr">
         <is>
-          <t>전일자 대차잔고 수량대비  오늘 엄청 ...[2] 진짜 대단합니다 오늘 같은날  1프로대 마이너스면 개미들 승리입니다
-상한가 홀딩 쭈욱 이어갑시다</t>
+          <t>외늠들 이제 9.6% 오늘 23만주매도... 크 이제 팔게 없나? 오늘은 조금파네. 다행이다. 이제 개인과 기관이 사면 오른다. 다만 외인이 마지막 발악 조심해야함.</t>
         </is>
       </c>
       <c r="H1506" t="n">
-        <v>416374950</v>
+        <v>416374913</v>
       </c>
     </row>
     <row r="1507">
@@ -58626,30 +58642,30 @@
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>동참했습니다!!</t>
+          <t>상한가주문</t>
         </is>
       </c>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>작지만 동참!!</t>
+          <t>81500</t>
         </is>
       </c>
       <c r="D1597" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E1597" t="n">
         <v>1</v>
       </c>
       <c r="F1597" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G1597" t="inlineStr">
         <is>
-          <t>동참했습니다!! 작지만 동참!!</t>
+          <t>상한가주문 81500</t>
         </is>
       </c>
       <c r="H1597" t="n">
-        <v>416307398</v>
+        <v>416307424</v>
       </c>
     </row>
     <row r="1598">
@@ -58660,30 +58676,30 @@
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>상한가주문</t>
+          <t>동참했습니다!!</t>
         </is>
       </c>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>81500</t>
+          <t>작지만 동참!!</t>
         </is>
       </c>
       <c r="D1598" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E1598" t="n">
         <v>1</v>
       </c>
       <c r="F1598" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1598" t="inlineStr">
         <is>
-          <t>상한가주문 81500</t>
+          <t>동참했습니다!! 작지만 동참!!</t>
         </is>
       </c>
       <c r="H1598" t="n">
-        <v>416307424</v>
+        <v>416307398</v>
       </c>
     </row>
     <row r="1599">
@@ -59194,66 +59210,66 @@
       </c>
       <c r="B1613" t="inlineStr">
         <is>
+          <t>나도 상한가 매도 동참</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>뭔진 모르지만 좋다니~</t>
+        </is>
+      </c>
+      <c r="D1613" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>나도 상한가 매도 동참 뭔진 모르지만 좋다니~</t>
+        </is>
+      </c>
+      <c r="H1613" t="n">
+        <v>416304412</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026.03.31 08:06</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
           <t>상한가 매도</t>
         </is>
       </c>
-      <c r="C1613" t="inlineStr">
+      <c r="C1614" t="inlineStr">
         <is>
           <t>완료
 할수있는거 다해봅시다</t>
         </is>
       </c>
-      <c r="D1613" t="n">
+      <c r="D1614" t="n">
         <v>14</v>
       </c>
-      <c r="E1613" t="n">
+      <c r="E1614" t="n">
         <v>0</v>
       </c>
-      <c r="F1613" t="n">
+      <c r="F1614" t="n">
         <v>31</v>
       </c>
-      <c r="G1613" t="inlineStr">
+      <c r="G1614" t="inlineStr">
         <is>
           <t>상한가 매도 완료
 할수있는거 다해봅시다</t>
         </is>
       </c>
-      <c r="H1613" t="n">
+      <c r="H1614" t="n">
         <v>416304315</v>
-      </c>
-    </row>
-    <row r="1614">
-      <c r="A1614" t="inlineStr">
-        <is>
-          <t>2026.03.31 08:06</t>
-        </is>
-      </c>
-      <c r="B1614" t="inlineStr">
-        <is>
-          <t>나도 상한가 매도 동참</t>
-        </is>
-      </c>
-      <c r="C1614" t="inlineStr">
-        <is>
-          <t>뭔진 모르지만 좋다니~</t>
-        </is>
-      </c>
-      <c r="D1614" t="n">
-        <v>11</v>
-      </c>
-      <c r="E1614" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1614" t="n">
-        <v>33</v>
-      </c>
-      <c r="G1614" t="inlineStr">
-        <is>
-          <t>나도 상한가 매도 동참 뭔진 모르지만 좋다니~</t>
-        </is>
-      </c>
-      <c r="H1614" t="n">
-        <v>416304412</v>
       </c>
     </row>
     <row r="1615">
@@ -67108,30 +67124,30 @@
       </c>
       <c r="B1830" t="inlineStr">
         <is>
-          <t>지저분 하다</t>
+          <t>나선 음전인데 ㄱㅊ??[1]</t>
         </is>
       </c>
       <c r="C1830" t="inlineStr">
         <is>
-          <t>매매 행태가 nxt 거래에서 이렇게 하락시킨다고 장난질이 심하네</t>
+          <t>어차피고평가인데 아침처럼 61000가는거아님?</t>
         </is>
       </c>
       <c r="D1830" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E1830" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F1830" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="G1830" t="inlineStr">
         <is>
-          <t>지저분 하다 매매 행태가 nxt 거래에서 이렇게 하락시킨다고 장난질이 심하네</t>
+          <t>나선 음전인데 ㄱㅊ??[1] 어차피고평가인데 아침처럼 61000가는거아님?</t>
         </is>
       </c>
       <c r="H1830" t="n">
-        <v>416143749</v>
+        <v>416143754</v>
       </c>
     </row>
     <row r="1831">
@@ -67142,30 +67158,30 @@
       </c>
       <c r="B1831" t="inlineStr">
         <is>
-          <t>나선 음전인데 ㄱㅊ??[1]</t>
+          <t>지저분 하다</t>
         </is>
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>어차피고평가인데 아침처럼 61000가는거아님?</t>
+          <t>매매 행태가 nxt 거래에서 이렇게 하락시킨다고 장난질이 심하네</t>
         </is>
       </c>
       <c r="D1831" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E1831" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F1831" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="G1831" t="inlineStr">
         <is>
-          <t>나선 음전인데 ㄱㅊ??[1] 어차피고평가인데 아침처럼 61000가는거아님?</t>
+          <t>지저분 하다 매매 행태가 nxt 거래에서 이렇게 하락시킨다고 장난질이 심하네</t>
         </is>
       </c>
       <c r="H1831" t="n">
-        <v>416143754</v>
+        <v>416143749</v>
       </c>
     </row>
     <row r="1832">
@@ -67656,68 +67672,68 @@
       </c>
       <c r="B1845" t="inlineStr">
         <is>
-          <t>미래이거[1]</t>
+          <t>다음주는 제발 71층 구조점..</t>
         </is>
       </c>
       <c r="C1845" t="inlineStr">
-        <is>
-          <t>넥장에서  한 7%정도  올리는거아냐  그럴꺼같네</t>
-        </is>
-      </c>
-      <c r="D1845" t="n">
-        <v>12</v>
-      </c>
-      <c r="E1845" t="n">
-        <v>7</v>
-      </c>
-      <c r="F1845" t="n">
-        <v>135</v>
-      </c>
-      <c r="G1845" t="inlineStr">
-        <is>
-          <t>미래이거[1] 넥장에서  한 7%정도  올리는거아냐  그럴꺼같네</t>
-        </is>
-      </c>
-      <c r="H1845" t="n">
-        <v>416135573</v>
-      </c>
-    </row>
-    <row r="1846">
-      <c r="A1846" t="inlineStr">
-        <is>
-          <t>2026.03.27 15:53</t>
-        </is>
-      </c>
-      <c r="B1846" t="inlineStr">
-        <is>
-          <t>다음주는 제발 71층 구조점..</t>
-        </is>
-      </c>
-      <c r="C1846" t="inlineStr">
         <is>
           <t>하..어제 70에 약손절로해서 다 쳐냈어야햇지만...
 미쳣다고 물을좀타서 70.5층으로...반층내려왔습니다..
 제발 구해주세요!!조금더 내려가 볼게요!!</t>
         </is>
       </c>
-      <c r="D1846" t="n">
+      <c r="D1845" t="n">
         <v>11</v>
       </c>
-      <c r="E1846" t="n">
+      <c r="E1845" t="n">
         <v>2</v>
       </c>
-      <c r="F1846" t="n">
+      <c r="F1845" t="n">
         <v>156</v>
       </c>
-      <c r="G1846" t="inlineStr">
+      <c r="G1845" t="inlineStr">
         <is>
           <t>다음주는 제발 71층 구조점.. 하..어제 70에 약손절로해서 다 쳐냈어야햇지만...
 미쳣다고 물을좀타서 70.5층으로...반층내려왔습니다..
 제발 구해주세요!!조금더 내려가 볼게요!!</t>
         </is>
       </c>
+      <c r="H1845" t="n">
+        <v>416135606</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>2026.03.27 15:53</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>미래이거[1]</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>넥장에서  한 7%정도  올리는거아냐  그럴꺼같네</t>
+        </is>
+      </c>
+      <c r="D1846" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>135</v>
+      </c>
+      <c r="G1846" t="inlineStr">
+        <is>
+          <t>미래이거[1] 넥장에서  한 7%정도  올리는거아냐  그럴꺼같네</t>
+        </is>
+      </c>
       <c r="H1846" t="n">
-        <v>416135606</v>
+        <v>416135573</v>
       </c>
     </row>
     <row r="1847">
@@ -69964,12 +69980,12 @@
       </c>
       <c r="B1908" t="inlineStr">
         <is>
-          <t>와 일하다 오니까 뭐고..</t>
+          <t>ㅋㅋㅋㅋㅋ</t>
         </is>
       </c>
       <c r="C1908" t="inlineStr">
         <is>
-          <t>아침에 판사람들은 우짜냐 이거</t>
+          <t xml:space="preserve">미래 너도 참.. </t>
         </is>
       </c>
       <c r="D1908" t="n">
@@ -69979,15 +69995,15 @@
         <v>0</v>
       </c>
       <c r="F1908" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G1908" t="inlineStr">
         <is>
-          <t>와 일하다 오니까 뭐고.. 아침에 판사람들은 우짜냐 이거</t>
+          <t xml:space="preserve">ㅋㅋㅋㅋㅋ 미래 너도 참.. </t>
         </is>
       </c>
       <c r="H1908" t="n">
-        <v>416116093</v>
+        <v>416116128</v>
       </c>
     </row>
     <row r="1909">
@@ -70032,12 +70048,12 @@
       </c>
       <c r="B1910" t="inlineStr">
         <is>
-          <t>ㅋㅋㅋㅋㅋ</t>
+          <t>와 일하다 오니까 뭐고..</t>
         </is>
       </c>
       <c r="C1910" t="inlineStr">
         <is>
-          <t xml:space="preserve">미래 너도 참.. </t>
+          <t>아침에 판사람들은 우짜냐 이거</t>
         </is>
       </c>
       <c r="D1910" t="n">
@@ -70047,15 +70063,15 @@
         <v>0</v>
       </c>
       <c r="F1910" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G1910" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㅋㅋㅋㅋㅋ 미래 너도 참.. </t>
+          <t>와 일하다 오니까 뭐고.. 아침에 판사람들은 우짜냐 이거</t>
         </is>
       </c>
       <c r="H1910" t="n">
-        <v>416116128</v>
+        <v>416116093</v>
       </c>
     </row>
     <row r="1911">
